--- a/data/Mappings/mapping_npri.xlsx
+++ b/data/Mappings/mapping_npri.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://polymtlca0-my.sharepoint.com/personal/marin_pellan_polymtlus_ca/Documents/Desktop/POST_DOC/Project/canada_metal_sustainability_db/data/Mappings/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mp_ma\OneDrive - polymtl\POST_DOC\CODE\metallican_db\data\Mappings\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="11_F25DC773A252ABDACC104887411C794C5BDE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6EF22D00-A37E-4E9A-BDEF-1D15B4FC287D}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79931472-8B2F-4982-8306-AF8D7544F4B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="2508" yWindow="2508" windowWidth="17280" windowHeight="8880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="mapping" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">LT!$A$1:$G$589</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">mapping!$A$1:$B$104</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1633" uniqueCount="770">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1631" uniqueCount="770">
   <si>
     <t>npri_id</t>
   </si>
@@ -2391,10 +2392,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2660,13 +2657,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B106"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:B104"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.5546875" customWidth="1"/>
+    <col min="1" max="1" width="10.54296875" customWidth="1"/>
+    <col min="2" max="2" width="17.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2674,847 +2672,836 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2">
+        <v>444</v>
+      </c>
+      <c r="B2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>1070</v>
+      </c>
+      <c r="B3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>1071</v>
+      </c>
+      <c r="B4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>1106</v>
+      </c>
+      <c r="B5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>1148</v>
+      </c>
+      <c r="B6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>1149</v>
+      </c>
+      <c r="B7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>1233</v>
+      </c>
+      <c r="B8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>1236</v>
+      </c>
+      <c r="B9" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>1303</v>
+      </c>
+      <c r="B10" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>1465</v>
+      </c>
+      <c r="B11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>1467</v>
+      </c>
+      <c r="B12" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>1471</v>
+      </c>
+      <c r="B13" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>1520</v>
+      </c>
+      <c r="B14" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>1568</v>
+      </c>
+      <c r="B15" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>1651</v>
+      </c>
+      <c r="B16" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>1941</v>
+      </c>
+      <c r="B17" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>2000</v>
+      </c>
+      <c r="B18" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>2038</v>
+      </c>
+      <c r="B19" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>2100</v>
+      </c>
+      <c r="B20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>2132</v>
+      </c>
+      <c r="B21" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>2372</v>
+      </c>
+      <c r="B22" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>2710</v>
+      </c>
+      <c r="B23" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>2740</v>
+      </c>
+      <c r="B24" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25">
+        <v>2978</v>
+      </c>
+      <c r="B25" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>2984</v>
+      </c>
+      <c r="B26" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <v>2986</v>
+      </c>
+      <c r="B27" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28">
+        <v>3060</v>
+      </c>
+      <c r="B28" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <v>3062</v>
+      </c>
+      <c r="B29" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30">
+        <v>3158</v>
+      </c>
+      <c r="B30" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A31">
+        <v>3197</v>
+      </c>
+      <c r="B31" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A32">
+        <v>3356</v>
+      </c>
+      <c r="B32" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A33">
+        <v>3406</v>
+      </c>
+      <c r="B33" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A34">
+        <v>3411</v>
+      </c>
+      <c r="B34" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A35">
+        <v>3598</v>
+      </c>
+      <c r="B35" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A36">
+        <v>3623</v>
+      </c>
+      <c r="B36" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A37">
+        <v>3649</v>
+      </c>
+      <c r="B37" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A38">
+        <v>3713</v>
+      </c>
+      <c r="B38" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A39">
+        <v>3802</v>
+      </c>
+      <c r="B39" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A40">
+        <v>3810</v>
+      </c>
+      <c r="B40" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A41">
+        <v>3824</v>
+      </c>
+      <c r="B41" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A42">
+        <v>3916</v>
+      </c>
+      <c r="B42" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A43">
         <v>3991</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B43" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>2132</v>
-      </c>
-      <c r="B3" t="s">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A44">
+        <v>4045</v>
+      </c>
+      <c r="B44" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A45">
+        <v>4169</v>
+      </c>
+      <c r="B45" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A46">
+        <v>4197</v>
+      </c>
+      <c r="B46" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A47">
+        <v>4778</v>
+      </c>
+      <c r="B47" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A48">
+        <v>4782</v>
+      </c>
+      <c r="B48" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A49">
+        <v>4806</v>
+      </c>
+      <c r="B49" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A50">
+        <v>4866</v>
+      </c>
+      <c r="B50" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A51">
+        <v>4868</v>
+      </c>
+      <c r="B51" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A52">
+        <v>5013</v>
+      </c>
+      <c r="B52" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A53">
+        <v>5102</v>
+      </c>
+      <c r="B53" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A54">
+        <v>5219</v>
+      </c>
+      <c r="B54" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A55">
+        <v>5448</v>
+      </c>
+      <c r="B55" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A56">
+        <v>5460</v>
+      </c>
+      <c r="B56" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A57">
+        <v>5510</v>
+      </c>
+      <c r="B57" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A58">
+        <v>5656</v>
+      </c>
+      <c r="B58" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A59">
+        <v>6093</v>
+      </c>
+      <c r="B59" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A60">
+        <v>6217</v>
+      </c>
+      <c r="B60" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A61">
+        <v>6344</v>
+      </c>
+      <c r="B61" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A62">
+        <v>8015</v>
+      </c>
+      <c r="B62" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A63">
+        <v>8757</v>
+      </c>
+      <c r="B63" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A64">
+        <v>8778</v>
+      </c>
+      <c r="B64" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A65">
+        <v>8783</v>
+      </c>
+      <c r="B65" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A66">
+        <v>8803</v>
+      </c>
+      <c r="B66" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A67">
+        <v>8807</v>
+      </c>
+      <c r="B67" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A68">
+        <v>10010</v>
+      </c>
+      <c r="B68" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A69">
+        <v>10153</v>
+      </c>
+      <c r="B69" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A70">
+        <v>10199</v>
+      </c>
+      <c r="B70" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A71">
+        <v>10201</v>
+      </c>
+      <c r="B71" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A72">
+        <v>10202</v>
+      </c>
+      <c r="B72" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A73">
+        <v>10203</v>
+      </c>
+      <c r="B73" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A74">
+        <v>10204</v>
+      </c>
+      <c r="B74" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A75">
+        <v>11123</v>
+      </c>
+      <c r="B75" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A76">
+        <v>11154</v>
+      </c>
+      <c r="B76" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A77">
+        <v>11454</v>
+      </c>
+      <c r="B77" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A78">
         <v>11588</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B78" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>11123</v>
-      </c>
-      <c r="B5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>6344</v>
-      </c>
-      <c r="B6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>3810</v>
-      </c>
-      <c r="B7" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A79">
+        <v>11794</v>
+      </c>
+      <c r="B79" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A80">
+        <v>11796</v>
+      </c>
+      <c r="B80" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A81">
+        <v>11867</v>
+      </c>
+      <c r="B81" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A82">
+        <v>11878</v>
+      </c>
+      <c r="B82" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A83">
+        <v>19397</v>
+      </c>
+      <c r="B83" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A84">
+        <v>20131</v>
+      </c>
+      <c r="B84" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A85">
+        <v>23273</v>
+      </c>
+      <c r="B85" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A86">
+        <v>24216</v>
+      </c>
+      <c r="B86" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A87">
+        <v>25188</v>
+      </c>
+      <c r="B87" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A88">
+        <v>25434</v>
+      </c>
+      <c r="B88" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A89">
+        <v>26132</v>
+      </c>
+      <c r="B89" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A90">
+        <v>26423</v>
+      </c>
+      <c r="B90" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A91">
+        <v>27063</v>
+      </c>
+      <c r="B91" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A92">
+        <v>27853</v>
+      </c>
+      <c r="B92" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A93">
+        <v>28726</v>
+      </c>
+      <c r="B93" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A94">
+        <v>28761</v>
+      </c>
+      <c r="B94" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A95">
+        <v>29072</v>
+      </c>
+      <c r="B95" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A96">
+        <v>29191</v>
+      </c>
+      <c r="B96" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A97">
+        <v>29548</v>
+      </c>
+      <c r="B97" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A98">
+        <v>29877</v>
+      </c>
+      <c r="B98" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A99">
+        <v>30798</v>
+      </c>
+      <c r="B99" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A100">
+        <v>32235</v>
+      </c>
+      <c r="B100" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A101">
+        <v>32933</v>
+      </c>
+      <c r="B101" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A102">
+        <v>33049</v>
+      </c>
+      <c r="B102" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A103">
+        <v>33819</v>
+      </c>
+      <c r="B103" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A104">
         <v>34014</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B104" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>11878</v>
-      </c>
-      <c r="B9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <v>1471</v>
-      </c>
-      <c r="B10" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11">
-        <v>2100</v>
-      </c>
-      <c r="B11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12">
-        <v>3062</v>
-      </c>
-      <c r="B12" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13">
-        <v>3060</v>
-      </c>
-      <c r="B13" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14">
-        <v>5219</v>
-      </c>
-      <c r="B14" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15">
-        <v>8807</v>
-      </c>
-      <c r="B15" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16">
-        <v>10010</v>
-      </c>
-      <c r="B16" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17">
-        <v>19397</v>
-      </c>
-      <c r="B17" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18">
-        <v>11154</v>
-      </c>
-      <c r="B18" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19">
-        <v>1233</v>
-      </c>
-      <c r="B19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20">
-        <v>3158</v>
-      </c>
-      <c r="B20" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21">
-        <v>1465</v>
-      </c>
-      <c r="B21" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22">
-        <v>25434</v>
-      </c>
-      <c r="B22" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23">
-        <v>5510</v>
-      </c>
-      <c r="B23" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24">
-        <v>5460</v>
-      </c>
-      <c r="B24" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25">
-        <v>10201</v>
-      </c>
-      <c r="B25" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26">
-        <v>3411</v>
-      </c>
-      <c r="B26" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A27">
-        <v>4169</v>
-      </c>
-      <c r="B27" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A28">
-        <v>10202</v>
-      </c>
-      <c r="B28" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A29">
-        <v>4778</v>
-      </c>
-      <c r="B29" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A30">
-        <v>4782</v>
-      </c>
-      <c r="B30" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A31">
-        <v>1520</v>
-      </c>
-      <c r="B31" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A32">
-        <v>29877</v>
-      </c>
-      <c r="B32" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A33">
-        <v>8757</v>
-      </c>
-      <c r="B33" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A34">
-        <v>28761</v>
-      </c>
-      <c r="B34" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A35">
-        <v>1303</v>
-      </c>
-      <c r="B35" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36">
-        <v>26423</v>
-      </c>
-      <c r="B36" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A37">
-        <v>444</v>
-      </c>
-      <c r="B37" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A38">
-        <v>26132</v>
-      </c>
-      <c r="B38" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A39">
-        <v>2986</v>
-      </c>
-      <c r="B39" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A40">
-        <v>1149</v>
-      </c>
-      <c r="B40" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A41">
-        <v>1070</v>
-      </c>
-      <c r="B41" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A42">
-        <v>3824</v>
-      </c>
-      <c r="B42" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A43">
-        <v>4868</v>
-      </c>
-      <c r="B43" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A44">
-        <v>10153</v>
-      </c>
-      <c r="B44" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A45">
-        <v>3197</v>
-      </c>
-      <c r="B45" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A46">
-        <v>1071</v>
-      </c>
-      <c r="B46" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A47">
-        <v>25188</v>
-      </c>
-      <c r="B47" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A48">
-        <v>3802</v>
-      </c>
-      <c r="B48" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A49">
-        <v>2038</v>
-      </c>
-      <c r="B49" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A50">
-        <v>8783</v>
-      </c>
-      <c r="B50" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A51">
-        <v>1941</v>
-      </c>
-      <c r="B51" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A52">
-        <v>8015</v>
-      </c>
-      <c r="B52" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A53">
-        <v>1236</v>
-      </c>
-      <c r="B53" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A54">
-        <v>32933</v>
-      </c>
-      <c r="B54" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A55">
-        <v>8778</v>
-      </c>
-      <c r="B55" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A56">
-        <v>2000</v>
-      </c>
-      <c r="B56" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A57">
-        <v>2740</v>
-      </c>
-      <c r="B57" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A58">
-        <v>3406</v>
-      </c>
-      <c r="B58" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A59">
-        <v>33049</v>
-      </c>
-      <c r="B59" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A60">
-        <v>1651</v>
-      </c>
-      <c r="B60" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A61">
-        <v>3916</v>
-      </c>
-      <c r="B61" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A62">
-        <v>11794</v>
-      </c>
-      <c r="B62" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A63">
-        <v>4806</v>
-      </c>
-      <c r="B63" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A64">
-        <v>5448</v>
-      </c>
-      <c r="B64" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A65">
-        <v>23273</v>
-      </c>
-      <c r="B65" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A66">
-        <v>5102</v>
-      </c>
-      <c r="B66" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A67">
-        <v>27853</v>
-      </c>
-      <c r="B67" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A68">
-        <v>6093</v>
-      </c>
-      <c r="B68" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A69">
-        <v>2984</v>
-      </c>
-      <c r="B69" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A70">
-        <v>3623</v>
-      </c>
-      <c r="B70" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A71">
-        <v>11867</v>
-      </c>
-      <c r="B71" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A72">
-        <v>5656</v>
-      </c>
-      <c r="B72" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A73">
-        <v>24216</v>
-      </c>
-      <c r="B73" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A74">
-        <v>3649</v>
-      </c>
-      <c r="B74" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A75">
-        <v>6217</v>
-      </c>
-      <c r="B75" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A76">
-        <v>2372</v>
-      </c>
-      <c r="B76" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A77">
-        <v>3713</v>
-      </c>
-      <c r="B77" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A78">
-        <v>2978</v>
-      </c>
-      <c r="B78" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A79">
-        <v>4197</v>
-      </c>
-      <c r="B79" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A80">
-        <v>2710</v>
-      </c>
-      <c r="B80" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A81">
-        <v>3598</v>
-      </c>
-      <c r="B81" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A82">
-        <v>28726</v>
-      </c>
-      <c r="B82" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A83">
-        <v>29191</v>
-      </c>
-      <c r="B83" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A84">
-        <v>29548</v>
-      </c>
-      <c r="B84" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A85">
-        <v>1568</v>
-      </c>
-      <c r="B85" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A86">
-        <v>8803</v>
-      </c>
-      <c r="B86" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A87">
-        <v>444</v>
-      </c>
-      <c r="B87" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A88">
-        <v>3356</v>
-      </c>
-      <c r="B88" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A89">
-        <v>1148</v>
-      </c>
-      <c r="B89" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A90">
-        <v>11454</v>
-      </c>
-      <c r="B90" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A91">
-        <v>29072</v>
-      </c>
-      <c r="B91" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A92">
-        <v>27063</v>
-      </c>
-      <c r="B92" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A93">
-        <v>30798</v>
-      </c>
-      <c r="B93" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A94">
-        <v>10203</v>
-      </c>
-      <c r="B94" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A95">
-        <v>4045</v>
-      </c>
-      <c r="B95" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A96">
-        <v>10204</v>
-      </c>
-      <c r="B96" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A97">
-        <v>32235</v>
-      </c>
-      <c r="B97" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A98">
-        <v>1106</v>
-      </c>
-      <c r="B98" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A99">
-        <v>1467</v>
-      </c>
-      <c r="B99" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A100">
-        <v>10199</v>
-      </c>
-      <c r="B100" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A101">
-        <v>3598</v>
-      </c>
-      <c r="B101" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A102">
-        <v>20131</v>
-      </c>
-      <c r="B102" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A103">
-        <v>5013</v>
-      </c>
-      <c r="B103" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A104">
-        <v>4866</v>
-      </c>
-      <c r="B104" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A105">
-        <v>11796</v>
-      </c>
-      <c r="B105" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A106">
-        <v>33819</v>
-      </c>
-      <c r="B106" t="s">
-        <v>77</v>
-      </c>
-    </row>
   </sheetData>
+  <autoFilter ref="A1:B104" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B104">
+      <sortCondition ref="A1:A104"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3523,18 +3510,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{556460DC-71F1-43FF-BD31-36D25365B781}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:G589"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="35.77734375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="63.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="63.6328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -3557,7 +3544,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="2" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>103</v>
       </c>
@@ -3580,7 +3567,7 @@
         <v>27.7777777777777</v>
       </c>
     </row>
-    <row r="3" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>106</v>
       </c>
@@ -3588,7 +3575,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="4" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>108</v>
       </c>
@@ -3611,7 +3598,7 @@
         <v>15.3846153846153</v>
       </c>
     </row>
-    <row r="5" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>111</v>
       </c>
@@ -3619,7 +3606,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="6" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>45</v>
       </c>
@@ -3642,7 +3629,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>45</v>
       </c>
@@ -3665,7 +3652,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>45</v>
       </c>
@@ -3688,7 +3675,7 @@
         <v>31.578947368421002</v>
       </c>
     </row>
-    <row r="9" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>68</v>
       </c>
@@ -3711,7 +3698,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="10" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>32</v>
       </c>
@@ -3734,7 +3721,7 @@
         <v>14.285714285714199</v>
       </c>
     </row>
-    <row r="11" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>32</v>
       </c>
@@ -3757,7 +3744,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="12" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>32</v>
       </c>
@@ -3780,7 +3767,7 @@
         <v>29.629629629629601</v>
       </c>
     </row>
-    <row r="13" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>120</v>
       </c>
@@ -3803,7 +3790,7 @@
         <v>52.173913043478201</v>
       </c>
     </row>
-    <row r="14" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>120</v>
       </c>
@@ -3826,7 +3813,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="15" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>81</v>
       </c>
@@ -3849,7 +3836,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="16" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>70</v>
       </c>
@@ -3872,7 +3859,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="17" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>128</v>
       </c>
@@ -3880,7 +3867,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>130</v>
       </c>
@@ -3888,7 +3875,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="19" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>132</v>
       </c>
@@ -3896,7 +3883,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="20" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>85</v>
       </c>
@@ -3919,7 +3906,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>85</v>
       </c>
@@ -3942,7 +3929,7 @@
         <v>23.529411764705799</v>
       </c>
     </row>
-    <row r="22" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>37</v>
       </c>
@@ -3965,7 +3952,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>47</v>
       </c>
@@ -3988,7 +3975,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>29</v>
       </c>
@@ -4011,7 +3998,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>29</v>
       </c>
@@ -4034,7 +4021,7 @@
         <v>11.1111111111111</v>
       </c>
     </row>
-    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>143</v>
       </c>
@@ -4057,7 +4044,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>143</v>
       </c>
@@ -4080,7 +4067,7 @@
         <v>10.5263157894736</v>
       </c>
     </row>
-    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>143</v>
       </c>
@@ -4103,7 +4090,7 @@
         <v>14.285714285714199</v>
       </c>
     </row>
-    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>143</v>
       </c>
@@ -4126,7 +4113,7 @@
         <v>18.181818181818102</v>
       </c>
     </row>
-    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>143</v>
       </c>
@@ -4149,7 +4136,7 @@
         <v>22.2222222222222</v>
       </c>
     </row>
-    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>143</v>
       </c>
@@ -4172,7 +4159,7 @@
         <v>7.8431372549019596</v>
       </c>
     </row>
-    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>143</v>
       </c>
@@ -4195,7 +4182,7 @@
         <v>19.047619047619001</v>
       </c>
     </row>
-    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>143</v>
       </c>
@@ -4218,7 +4205,7 @@
         <v>23.529411764705799</v>
       </c>
     </row>
-    <row r="34" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>143</v>
       </c>
@@ -4241,7 +4228,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="35" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>44</v>
       </c>
@@ -4264,7 +4251,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="36" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>44</v>
       </c>
@@ -4287,7 +4274,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="37" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>44</v>
       </c>
@@ -4310,7 +4297,7 @@
         <v>23.076923076922998</v>
       </c>
     </row>
-    <row r="38" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>40</v>
       </c>
@@ -4333,7 +4320,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="39" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>40</v>
       </c>
@@ -4356,7 +4343,7 @@
         <v>66.6666666666666</v>
       </c>
     </row>
-    <row r="40" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>161</v>
       </c>
@@ -4364,7 +4351,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="41" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>163</v>
       </c>
@@ -4372,7 +4359,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="42" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>91</v>
       </c>
@@ -4395,7 +4382,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="43" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>91</v>
       </c>
@@ -4418,7 +4405,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="44" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>53</v>
       </c>
@@ -4441,7 +4428,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="45" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>72</v>
       </c>
@@ -4464,7 +4451,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="46" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>72</v>
       </c>
@@ -4487,7 +4474,7 @@
         <v>14.285714285714199</v>
       </c>
     </row>
-    <row r="47" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>71</v>
       </c>
@@ -4510,7 +4497,7 @@
         <v>52.173913043478201</v>
       </c>
     </row>
-    <row r="48" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>71</v>
       </c>
@@ -4533,7 +4520,7 @@
         <v>59.090909090909001</v>
       </c>
     </row>
-    <row r="49" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>71</v>
       </c>
@@ -4556,7 +4543,7 @@
         <v>13.043478260869501</v>
       </c>
     </row>
-    <row r="50" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>71</v>
       </c>
@@ -4579,7 +4566,7 @@
         <v>27.906976744186</v>
       </c>
     </row>
-    <row r="51" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>71</v>
       </c>
@@ -4602,7 +4589,7 @@
         <v>38.709677419354797</v>
       </c>
     </row>
-    <row r="52" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>38</v>
       </c>
@@ -4625,7 +4612,7 @@
         <v>56.521739130434703</v>
       </c>
     </row>
-    <row r="53" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>38</v>
       </c>
@@ -4648,7 +4635,7 @@
         <v>54.545454545454497</v>
       </c>
     </row>
-    <row r="54" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>38</v>
       </c>
@@ -4671,7 +4658,7 @@
         <v>8.6956521739130395</v>
       </c>
     </row>
-    <row r="55" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>38</v>
       </c>
@@ -4694,7 +4681,7 @@
         <v>32.558139534883701</v>
       </c>
     </row>
-    <row r="56" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>38</v>
       </c>
@@ -4717,7 +4704,7 @@
         <v>38.709677419354797</v>
       </c>
     </row>
-    <row r="57" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>54</v>
       </c>
@@ -4740,7 +4727,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="58" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>74</v>
       </c>
@@ -4763,7 +4750,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="59" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>74</v>
       </c>
@@ -4786,7 +4773,7 @@
         <v>76.470588235294102</v>
       </c>
     </row>
-    <row r="60" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>74</v>
       </c>
@@ -4809,7 +4796,7 @@
         <v>30.769230769230699</v>
       </c>
     </row>
-    <row r="61" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>74</v>
       </c>
@@ -4832,7 +4819,7 @@
         <v>29.090909090909001</v>
       </c>
     </row>
-    <row r="62" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>74</v>
       </c>
@@ -4855,7 +4842,7 @@
         <v>29.090909090909001</v>
       </c>
     </row>
-    <row r="63" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>74</v>
       </c>
@@ -4878,7 +4865,7 @@
         <v>23.8095238095238</v>
       </c>
     </row>
-    <row r="64" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>74</v>
       </c>
@@ -4901,7 +4888,7 @@
         <v>37.5</v>
       </c>
     </row>
-    <row r="65" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>74</v>
       </c>
@@ -4924,7 +4911,7 @@
         <v>27.450980392156801</v>
       </c>
     </row>
-    <row r="66" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>74</v>
       </c>
@@ -4947,7 +4934,7 @@
         <v>20.689655172413701</v>
       </c>
     </row>
-    <row r="67" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>74</v>
       </c>
@@ -4970,7 +4957,7 @@
         <v>26.315789473684202</v>
       </c>
     </row>
-    <row r="68" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>74</v>
       </c>
@@ -4993,7 +4980,7 @@
         <v>30.769230769230699</v>
       </c>
     </row>
-    <row r="69" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>57</v>
       </c>
@@ -5016,7 +5003,7 @@
         <v>27.272727272727199</v>
       </c>
     </row>
-    <row r="70" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>57</v>
       </c>
@@ -5039,7 +5026,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="71" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>194</v>
       </c>
@@ -5047,7 +5034,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="72" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>2</v>
       </c>
@@ -5070,7 +5057,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="73" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>2</v>
       </c>
@@ -5093,7 +5080,7 @@
         <v>25.806451612903199</v>
       </c>
     </row>
-    <row r="74" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>2</v>
       </c>
@@ -5116,7 +5103,7 @@
         <v>24.2424242424242</v>
       </c>
     </row>
-    <row r="75" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>2</v>
       </c>
@@ -5139,7 +5126,7 @@
         <v>22.2222222222222</v>
       </c>
     </row>
-    <row r="76" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>2</v>
       </c>
@@ -5162,7 +5149,7 @@
         <v>22.2222222222222</v>
       </c>
     </row>
-    <row r="77" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>2</v>
       </c>
@@ -5185,7 +5172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>2</v>
       </c>
@@ -5208,7 +5195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>2</v>
       </c>
@@ -5231,7 +5218,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="80" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>2</v>
       </c>
@@ -5254,7 +5241,7 @@
         <v>6.6666666666666696</v>
       </c>
     </row>
-    <row r="81" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>2</v>
       </c>
@@ -5277,7 +5264,7 @@
         <v>27.272727272727199</v>
       </c>
     </row>
-    <row r="82" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>207</v>
       </c>
@@ -5285,7 +5272,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="83" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>209</v>
       </c>
@@ -5293,7 +5280,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="84" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>211</v>
       </c>
@@ -5301,7 +5288,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="85" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>43</v>
       </c>
@@ -5324,7 +5311,7 @@
         <v>55.172413793103402</v>
       </c>
     </row>
-    <row r="86" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>215</v>
       </c>
@@ -5332,7 +5319,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="87" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>217</v>
       </c>
@@ -5340,7 +5327,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="88" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>219</v>
       </c>
@@ -5348,7 +5335,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="89" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>221</v>
       </c>
@@ -5356,7 +5343,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="90" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>223</v>
       </c>
@@ -5364,7 +5351,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="91" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>225</v>
       </c>
@@ -5372,7 +5359,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="92" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>16</v>
       </c>
@@ -5395,7 +5382,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="93" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>84</v>
       </c>
@@ -5418,7 +5405,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="94" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>39</v>
       </c>
@@ -5441,7 +5428,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="95" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>233</v>
       </c>
@@ -5464,7 +5451,7 @@
         <v>19.047619047619001</v>
       </c>
     </row>
-    <row r="96" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>236</v>
       </c>
@@ -5487,7 +5474,7 @@
         <v>9.0909090909090899</v>
       </c>
     </row>
-    <row r="97" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>236</v>
       </c>
@@ -5510,7 +5497,7 @@
         <v>38.461538461538403</v>
       </c>
     </row>
-    <row r="98" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>240</v>
       </c>
@@ -5518,7 +5505,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="99" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>242</v>
       </c>
@@ -5526,7 +5513,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="100" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>244</v>
       </c>
@@ -5534,7 +5521,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="101" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>246</v>
       </c>
@@ -5542,7 +5529,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="102" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>248</v>
       </c>
@@ -5550,7 +5537,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="103" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>250</v>
       </c>
@@ -5558,7 +5545,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="104" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>94</v>
       </c>
@@ -5581,7 +5568,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="105" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>79</v>
       </c>
@@ -5604,7 +5591,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="106" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>48</v>
       </c>
@@ -5627,7 +5614,7 @@
         <v>20.689655172413701</v>
       </c>
     </row>
-    <row r="107" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>48</v>
       </c>
@@ -5650,7 +5637,7 @@
         <v>66.6666666666666</v>
       </c>
     </row>
-    <row r="108" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>257</v>
       </c>
@@ -5658,7 +5645,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="109" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>259</v>
       </c>
@@ -5666,7 +5653,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="110" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>261</v>
       </c>
@@ -5674,7 +5661,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="111" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>263</v>
       </c>
@@ -5682,7 +5669,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="112" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>265</v>
       </c>
@@ -5690,7 +5677,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="113" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>267</v>
       </c>
@@ -5698,7 +5685,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="114" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>269</v>
       </c>
@@ -5721,7 +5708,7 @@
         <v>23.529411764705799</v>
       </c>
     </row>
-    <row r="115" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>269</v>
       </c>
@@ -5744,7 +5731,7 @@
         <v>33.3333333333333</v>
       </c>
     </row>
-    <row r="116" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>269</v>
       </c>
@@ -5767,7 +5754,7 @@
         <v>20.8333333333333</v>
       </c>
     </row>
-    <row r="117" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>269</v>
       </c>
@@ -5790,7 +5777,7 @@
         <v>22.727272727272702</v>
       </c>
     </row>
-    <row r="118" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>269</v>
       </c>
@@ -5813,7 +5800,7 @@
         <v>22.857142857142801</v>
       </c>
     </row>
-    <row r="119" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>275</v>
       </c>
@@ -5821,7 +5808,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="120" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>277</v>
       </c>
@@ -5829,7 +5816,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="121" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>279</v>
       </c>
@@ -5852,7 +5839,7 @@
         <v>18.75</v>
       </c>
     </row>
-    <row r="122" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>282</v>
       </c>
@@ -5860,7 +5847,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="123" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>284</v>
       </c>
@@ -5868,7 +5855,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="124" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>286</v>
       </c>
@@ -5876,7 +5863,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="125" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>288</v>
       </c>
@@ -5899,7 +5886,7 @@
         <v>9.0909090909090899</v>
       </c>
     </row>
-    <row r="126" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>288</v>
       </c>
@@ -5922,7 +5909,7 @@
         <v>11.764705882352899</v>
       </c>
     </row>
-    <row r="127" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>288</v>
       </c>
@@ -5945,7 +5932,7 @@
         <v>21.428571428571399</v>
       </c>
     </row>
-    <row r="128" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>8</v>
       </c>
@@ -5968,7 +5955,7 @@
         <v>20.5128205128205</v>
       </c>
     </row>
-    <row r="129" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>8</v>
       </c>
@@ -5991,7 +5978,7 @@
         <v>29.787234042553099</v>
       </c>
     </row>
-    <row r="130" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>6</v>
       </c>
@@ -6014,7 +6001,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="131" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>6</v>
       </c>
@@ -6037,7 +6024,7 @@
         <v>86.956521739130395</v>
       </c>
     </row>
-    <row r="132" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>6</v>
       </c>
@@ -6060,7 +6047,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="133" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>6</v>
       </c>
@@ -6083,7 +6070,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="134" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>6</v>
       </c>
@@ -6106,7 +6093,7 @@
         <v>18.181818181818102</v>
       </c>
     </row>
-    <row r="135" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>6</v>
       </c>
@@ -6129,7 +6116,7 @@
         <v>21.428571428571399</v>
       </c>
     </row>
-    <row r="136" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>6</v>
       </c>
@@ -6152,7 +6139,7 @@
         <v>19.672131147540899</v>
       </c>
     </row>
-    <row r="137" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>6</v>
       </c>
@@ -6175,7 +6162,7 @@
         <v>25.806451612903199</v>
       </c>
     </row>
-    <row r="138" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>6</v>
       </c>
@@ -6198,7 +6185,7 @@
         <v>22.2222222222222</v>
       </c>
     </row>
-    <row r="139" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>6</v>
       </c>
@@ -6221,7 +6208,7 @@
         <v>23.8095238095238</v>
       </c>
     </row>
-    <row r="140" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>93</v>
       </c>
@@ -6244,7 +6231,7 @@
         <v>60.606060606060602</v>
       </c>
     </row>
-    <row r="141" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>93</v>
       </c>
@@ -6267,7 +6254,7 @@
         <v>46.511627906976699</v>
       </c>
     </row>
-    <row r="142" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>93</v>
       </c>
@@ -6290,7 +6277,7 @@
         <v>31.25</v>
       </c>
     </row>
-    <row r="143" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>77</v>
       </c>
@@ -6313,7 +6300,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="144" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>77</v>
       </c>
@@ -6336,7 +6323,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="145" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>55</v>
       </c>
@@ -6359,7 +6346,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="146" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>15</v>
       </c>
@@ -6382,7 +6369,7 @@
         <v>62.857142857142797</v>
       </c>
     </row>
-    <row r="147" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>15</v>
       </c>
@@ -6405,7 +6392,7 @@
         <v>48.8888888888888</v>
       </c>
     </row>
-    <row r="148" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>15</v>
       </c>
@@ -6428,7 +6415,7 @@
         <v>58.823529411764703</v>
       </c>
     </row>
-    <row r="149" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>87</v>
       </c>
@@ -6451,7 +6438,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="150" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>50</v>
       </c>
@@ -6474,7 +6461,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="151" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>306</v>
       </c>
@@ -6482,7 +6469,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="152" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>308</v>
       </c>
@@ -6490,7 +6477,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="153" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>310</v>
       </c>
@@ -6498,7 +6485,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="154" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>312</v>
       </c>
@@ -6506,7 +6493,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="155" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>314</v>
       </c>
@@ -6514,7 +6501,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="156" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>316</v>
       </c>
@@ -6522,7 +6509,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="157" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>318</v>
       </c>
@@ -6530,7 +6517,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="158" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>320</v>
       </c>
@@ -6538,7 +6525,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="159" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>322</v>
       </c>
@@ -6546,7 +6533,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="160" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>324</v>
       </c>
@@ -6554,7 +6541,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="161" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>326</v>
       </c>
@@ -6562,7 +6549,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="162" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>328</v>
       </c>
@@ -6570,7 +6557,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="163" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>330</v>
       </c>
@@ -6578,7 +6565,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="164" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>332</v>
       </c>
@@ -6601,7 +6588,7 @@
         <v>27.118644067796598</v>
       </c>
     </row>
-    <row r="165" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>332</v>
       </c>
@@ -6624,7 +6611,7 @@
         <v>28.571428571428498</v>
       </c>
     </row>
-    <row r="166" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>332</v>
       </c>
@@ -6647,7 +6634,7 @@
         <v>16.326530612244799</v>
       </c>
     </row>
-    <row r="167" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>332</v>
       </c>
@@ -6670,7 +6657,7 @@
         <v>4.6511627906976596</v>
       </c>
     </row>
-    <row r="168" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>332</v>
       </c>
@@ -6693,7 +6680,7 @@
         <v>30.136986301369799</v>
       </c>
     </row>
-    <row r="169" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>336</v>
       </c>
@@ -6716,7 +6703,7 @@
         <v>26.6666666666666</v>
       </c>
     </row>
-    <row r="170" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>339</v>
       </c>
@@ -6739,7 +6726,7 @@
         <v>57.142857142857103</v>
       </c>
     </row>
-    <row r="171" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>339</v>
       </c>
@@ -6762,7 +6749,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="172" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>26</v>
       </c>
@@ -6785,7 +6772,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="173" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>26</v>
       </c>
@@ -6808,7 +6795,7 @@
         <v>11.4285714285714</v>
       </c>
     </row>
-    <row r="174" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>58</v>
       </c>
@@ -6831,7 +6818,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="175" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>41</v>
       </c>
@@ -6854,7 +6841,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="176" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
         <v>41</v>
       </c>
@@ -6877,7 +6864,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="177" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
         <v>348</v>
       </c>
@@ -6900,7 +6887,7 @@
         <v>15.0537634408602</v>
       </c>
     </row>
-    <row r="178" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
         <v>59</v>
       </c>
@@ -6923,7 +6910,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
         <v>59</v>
       </c>
@@ -6946,7 +6933,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="180" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
         <v>59</v>
       </c>
@@ -6969,7 +6956,7 @@
         <v>17.391304347826001</v>
       </c>
     </row>
-    <row r="181" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
         <v>59</v>
       </c>
@@ -6992,7 +6979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
         <v>59</v>
       </c>
@@ -7015,7 +7002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
         <v>353</v>
       </c>
@@ -7038,7 +7025,7 @@
         <v>16.6666666666666</v>
       </c>
     </row>
-    <row r="184" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
         <v>353</v>
       </c>
@@ -7061,7 +7048,7 @@
         <v>23.529411764705799</v>
       </c>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
         <v>353</v>
       </c>
@@ -7084,7 +7071,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="186" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
         <v>353</v>
       </c>
@@ -7107,7 +7094,7 @@
         <v>22.2222222222222</v>
       </c>
     </row>
-    <row r="187" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
         <v>359</v>
       </c>
@@ -7130,7 +7117,7 @@
         <v>26.229508196721302</v>
       </c>
     </row>
-    <row r="188" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
         <v>359</v>
       </c>
@@ -7153,7 +7140,7 @@
         <v>11.1111111111111</v>
       </c>
     </row>
-    <row r="189" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
         <v>359</v>
       </c>
@@ -7176,7 +7163,7 @@
         <v>5.4054054054053999</v>
       </c>
     </row>
-    <row r="190" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
         <v>67</v>
       </c>
@@ -7199,7 +7186,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="191" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
         <v>42</v>
       </c>
@@ -7222,7 +7209,7 @@
         <v>58.3333333333333</v>
       </c>
     </row>
-    <row r="192" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
         <v>42</v>
       </c>
@@ -7245,7 +7232,7 @@
         <v>21.428571428571399</v>
       </c>
     </row>
-    <row r="193" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
         <v>4</v>
       </c>
@@ -7268,7 +7255,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="194" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
         <v>4</v>
       </c>
@@ -7291,7 +7278,7 @@
         <v>14.814814814814801</v>
       </c>
     </row>
-    <row r="195" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
         <v>4</v>
       </c>
@@ -7314,7 +7301,7 @@
         <v>54.545454545454497</v>
       </c>
     </row>
-    <row r="196" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
         <v>369</v>
       </c>
@@ -7337,7 +7324,7 @@
         <v>25.806451612903199</v>
       </c>
     </row>
-    <row r="197" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
         <v>369</v>
       </c>
@@ -7360,7 +7347,7 @@
         <v>33.3333333333333</v>
       </c>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
         <v>369</v>
       </c>
@@ -7383,7 +7370,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="199" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
         <v>369</v>
       </c>
@@ -7406,7 +7393,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="200" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
         <v>62</v>
       </c>
@@ -7429,7 +7416,7 @@
         <v>14.814814814814801</v>
       </c>
     </row>
-    <row r="201" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
         <v>62</v>
       </c>
@@ -7452,7 +7439,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="202" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
         <v>18</v>
       </c>
@@ -7475,7 +7462,7 @@
         <v>14.285714285714199</v>
       </c>
     </row>
-    <row r="203" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
         <v>18</v>
       </c>
@@ -7498,7 +7485,7 @@
         <v>28.571428571428498</v>
       </c>
     </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
         <v>18</v>
       </c>
@@ -7521,7 +7508,7 @@
         <v>18.518518518518501</v>
       </c>
     </row>
-    <row r="205" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
         <v>18</v>
       </c>
@@ -7544,7 +7531,7 @@
         <v>18.181818181818102</v>
       </c>
     </row>
-    <row r="206" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
         <v>51</v>
       </c>
@@ -7567,7 +7554,7 @@
         <v>14.285714285714199</v>
       </c>
     </row>
-    <row r="207" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
         <v>51</v>
       </c>
@@ -7590,7 +7577,7 @@
         <v>11.1111111111111</v>
       </c>
     </row>
-    <row r="208" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
         <v>51</v>
       </c>
@@ -7613,7 +7600,7 @@
         <v>16.6666666666666</v>
       </c>
     </row>
-    <row r="209" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
         <v>51</v>
       </c>
@@ -7636,7 +7623,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="210" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
         <v>377</v>
       </c>
@@ -7644,7 +7631,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="211" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
         <v>379</v>
       </c>
@@ -7652,7 +7639,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="212" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
         <v>381</v>
       </c>
@@ -7660,7 +7647,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="213" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
         <v>383</v>
       </c>
@@ -7668,7 +7655,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="214" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
         <v>385</v>
       </c>
@@ -7676,7 +7663,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="215" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
         <v>387</v>
       </c>
@@ -7684,7 +7671,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="216" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
         <v>389</v>
       </c>
@@ -7692,7 +7679,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="217" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
         <v>391</v>
       </c>
@@ -7700,7 +7687,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="218" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
         <v>393</v>
       </c>
@@ -7708,7 +7695,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="219" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
         <v>30</v>
       </c>
@@ -7731,7 +7718,7 @@
         <v>28.9156626506024</v>
       </c>
     </row>
-    <row r="220" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
         <v>30</v>
       </c>
@@ -7754,7 +7741,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="221" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
         <v>397</v>
       </c>
@@ -7777,7 +7764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
         <v>397</v>
       </c>
@@ -7800,7 +7787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
         <v>397</v>
       </c>
@@ -7823,7 +7810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
         <v>88</v>
       </c>
@@ -7846,7 +7833,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="225" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
         <v>403</v>
       </c>
@@ -7869,7 +7856,7 @@
         <v>57.142857142857103</v>
       </c>
     </row>
-    <row r="226" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
         <v>403</v>
       </c>
@@ -7892,7 +7879,7 @@
         <v>21.428571428571399</v>
       </c>
     </row>
-    <row r="227" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
         <v>403</v>
       </c>
@@ -7915,7 +7902,7 @@
         <v>57.142857142857103</v>
       </c>
     </row>
-    <row r="228" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
         <v>14</v>
       </c>
@@ -7938,7 +7925,7 @@
         <v>31.25</v>
       </c>
     </row>
-    <row r="229" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
         <v>14</v>
       </c>
@@ -7961,7 +7948,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="230" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
         <v>14</v>
       </c>
@@ -7984,7 +7971,7 @@
         <v>23.529411764705799</v>
       </c>
     </row>
-    <row r="231" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
         <v>406</v>
       </c>
@@ -7992,7 +7979,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="232" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
         <v>25</v>
       </c>
@@ -8015,7 +8002,7 @@
         <v>57.142857142857103</v>
       </c>
     </row>
-    <row r="233" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
         <v>25</v>
       </c>
@@ -8038,7 +8025,7 @@
         <v>21.428571428571399</v>
       </c>
     </row>
-    <row r="234" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
         <v>25</v>
       </c>
@@ -8061,7 +8048,7 @@
         <v>57.142857142857103</v>
       </c>
     </row>
-    <row r="235" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
         <v>409</v>
       </c>
@@ -8069,7 +8056,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="236" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
         <v>411</v>
       </c>
@@ -8077,7 +8064,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="237" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
         <v>413</v>
       </c>
@@ -8100,7 +8087,7 @@
         <v>9.0909090909090899</v>
       </c>
     </row>
-    <row r="238" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
         <v>413</v>
       </c>
@@ -8123,7 +8110,7 @@
         <v>9.5238095238095095</v>
       </c>
     </row>
-    <row r="239" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
         <v>415</v>
       </c>
@@ -8146,7 +8133,7 @@
         <v>26.6666666666666</v>
       </c>
     </row>
-    <row r="240" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
         <v>415</v>
       </c>
@@ -8169,7 +8156,7 @@
         <v>37.037037037037003</v>
       </c>
     </row>
-    <row r="241" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
         <v>417</v>
       </c>
@@ -8192,7 +8179,7 @@
         <v>33.3333333333333</v>
       </c>
     </row>
-    <row r="242" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
         <v>64</v>
       </c>
@@ -8215,7 +8202,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="243" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
         <v>422</v>
       </c>
@@ -8223,7 +8210,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="244" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
         <v>95</v>
       </c>
@@ -8246,7 +8233,7 @@
         <v>66.6666666666666</v>
       </c>
     </row>
-    <row r="245" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
         <v>95</v>
       </c>
@@ -8269,7 +8256,7 @@
         <v>19.354838709677399</v>
       </c>
     </row>
-    <row r="246" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
         <v>17</v>
       </c>
@@ -8292,7 +8279,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="247" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
         <v>17</v>
       </c>
@@ -8315,7 +8302,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
         <v>17</v>
       </c>
@@ -8338,7 +8325,7 @@
         <v>21.052631578947299</v>
       </c>
     </row>
-    <row r="249" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
         <v>17</v>
       </c>
@@ -8361,7 +8348,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="250" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
         <v>52</v>
       </c>
@@ -8384,7 +8371,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="251" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
         <v>52</v>
       </c>
@@ -8407,7 +8394,7 @@
         <v>21.052631578947299</v>
       </c>
     </row>
-    <row r="252" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
         <v>52</v>
       </c>
@@ -8430,7 +8417,7 @@
         <v>36.363636363636303</v>
       </c>
     </row>
-    <row r="253" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
         <v>52</v>
       </c>
@@ -8453,7 +8440,7 @@
         <v>23.529411764705799</v>
       </c>
     </row>
-    <row r="254" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
         <v>76</v>
       </c>
@@ -8476,7 +8463,7 @@
         <v>72.727272727272705</v>
       </c>
     </row>
-    <row r="255" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
         <v>435</v>
       </c>
@@ -8499,7 +8486,7 @@
         <v>64.285714285714207</v>
       </c>
     </row>
-    <row r="256" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
         <v>435</v>
       </c>
@@ -8522,7 +8509,7 @@
         <v>28.571428571428498</v>
       </c>
     </row>
-    <row r="257" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
         <v>437</v>
       </c>
@@ -8530,7 +8517,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="258" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
         <v>439</v>
       </c>
@@ -8553,7 +8540,7 @@
         <v>44.4444444444444</v>
       </c>
     </row>
-    <row r="259" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
         <v>441</v>
       </c>
@@ -8576,7 +8563,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="260" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
         <v>441</v>
       </c>
@@ -8599,7 +8586,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="261" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
         <v>441</v>
       </c>
@@ -8622,7 +8609,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="262" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
         <v>441</v>
       </c>
@@ -8645,7 +8632,7 @@
         <v>8.4507042253521103</v>
       </c>
     </row>
-    <row r="263" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
         <v>441</v>
       </c>
@@ -8668,7 +8655,7 @@
         <v>35.443037974683499</v>
       </c>
     </row>
-    <row r="264" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
         <v>441</v>
       </c>
@@ -8691,7 +8678,7 @@
         <v>33.802816901408399</v>
       </c>
     </row>
-    <row r="265" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
         <v>441</v>
       </c>
@@ -8714,7 +8701,7 @@
         <v>37.931034482758598</v>
       </c>
     </row>
-    <row r="266" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
         <v>441</v>
       </c>
@@ -8737,7 +8724,7 @@
         <v>39.285714285714199</v>
       </c>
     </row>
-    <row r="267" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
         <v>441</v>
       </c>
@@ -8760,7 +8747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="268" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
         <v>450</v>
       </c>
@@ -8783,7 +8770,7 @@
         <v>25.6410256410256</v>
       </c>
     </row>
-    <row r="269" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
         <v>450</v>
       </c>
@@ -8806,7 +8793,7 @@
         <v>24.5614035087719</v>
       </c>
     </row>
-    <row r="270" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
         <v>450</v>
       </c>
@@ -8829,7 +8816,7 @@
         <v>20.689655172413701</v>
       </c>
     </row>
-    <row r="271" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
         <v>450</v>
       </c>
@@ -8852,7 +8839,7 @@
         <v>8.6956521739130395</v>
       </c>
     </row>
-    <row r="272" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
         <v>450</v>
       </c>
@@ -8875,7 +8862,7 @@
         <v>26.415094339622598</v>
       </c>
     </row>
-    <row r="273" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
         <v>452</v>
       </c>
@@ -8883,7 +8870,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="274" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
         <v>454</v>
       </c>
@@ -8891,7 +8878,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="275" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
         <v>456</v>
       </c>
@@ -8914,7 +8901,7 @@
         <v>21.276595744680801</v>
       </c>
     </row>
-    <row r="276" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
         <v>456</v>
       </c>
@@ -8937,7 +8924,7 @@
         <v>19.047619047619001</v>
       </c>
     </row>
-    <row r="277" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
         <v>456</v>
       </c>
@@ -8960,7 +8947,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="278" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
         <v>456</v>
       </c>
@@ -8983,7 +8970,7 @@
         <v>42.105263157894697</v>
       </c>
     </row>
-    <row r="279" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
         <v>458</v>
       </c>
@@ -8991,7 +8978,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="280" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
         <v>460</v>
       </c>
@@ -8999,7 +8986,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="281" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
         <v>462</v>
       </c>
@@ -9022,7 +9009,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="282" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
         <v>462</v>
       </c>
@@ -9045,7 +9032,7 @@
         <v>27.586206896551701</v>
       </c>
     </row>
-    <row r="283" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
         <v>462</v>
       </c>
@@ -9068,7 +9055,7 @@
         <v>26.315789473684202</v>
       </c>
     </row>
-    <row r="284" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
         <v>462</v>
       </c>
@@ -9091,7 +9078,7 @@
         <v>28.571428571428498</v>
       </c>
     </row>
-    <row r="285" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
         <v>462</v>
       </c>
@@ -9114,7 +9101,7 @@
         <v>26.229508196721302</v>
       </c>
     </row>
-    <row r="286" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
         <v>462</v>
       </c>
@@ -9137,7 +9124,7 @@
         <v>32.258064516128997</v>
       </c>
     </row>
-    <row r="287" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
         <v>462</v>
       </c>
@@ -9160,7 +9147,7 @@
         <v>22.2222222222222</v>
       </c>
     </row>
-    <row r="288" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
         <v>462</v>
       </c>
@@ -9183,7 +9170,7 @@
         <v>23.8095238095238</v>
       </c>
     </row>
-    <row r="289" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
         <v>11</v>
       </c>
@@ -9206,7 +9193,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="290" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
         <v>11</v>
       </c>
@@ -9229,7 +9216,7 @@
         <v>21.052631578947299</v>
       </c>
     </row>
-    <row r="291" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
         <v>11</v>
       </c>
@@ -9252,7 +9239,7 @@
         <v>21.428571428571399</v>
       </c>
     </row>
-    <row r="292" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
         <v>11</v>
       </c>
@@ -9275,7 +9262,7 @@
         <v>22.2222222222222</v>
       </c>
     </row>
-    <row r="293" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
         <v>11</v>
       </c>
@@ -9298,7 +9285,7 @@
         <v>11.764705882352899</v>
       </c>
     </row>
-    <row r="294" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
         <v>11</v>
       </c>
@@ -9321,7 +9308,7 @@
         <v>19.047619047619001</v>
       </c>
     </row>
-    <row r="295" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
         <v>11</v>
       </c>
@@ -9344,7 +9331,7 @@
         <v>23.529411764705799</v>
       </c>
     </row>
-    <row r="296" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
         <v>11</v>
       </c>
@@ -9367,7 +9354,7 @@
         <v>18.75</v>
       </c>
     </row>
-    <row r="297" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
         <v>465</v>
       </c>
@@ -9375,7 +9362,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="298" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
         <v>467</v>
       </c>
@@ -9398,7 +9385,7 @@
         <v>24.2424242424242</v>
       </c>
     </row>
-    <row r="299" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
         <v>469</v>
       </c>
@@ -9406,7 +9393,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="300" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
         <v>471</v>
       </c>
@@ -9414,7 +9401,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="301" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
         <v>7</v>
       </c>
@@ -9437,7 +9424,7 @@
         <v>42.857142857142797</v>
       </c>
     </row>
-    <row r="302" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
         <v>475</v>
       </c>
@@ -9445,7 +9432,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="303" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
         <v>477</v>
       </c>
@@ -9453,7 +9440,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="304" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
         <v>479</v>
       </c>
@@ -9461,7 +9448,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="305" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
         <v>481</v>
       </c>
@@ -9469,7 +9456,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="306" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
         <v>483</v>
       </c>
@@ -9477,7 +9464,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="307" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
         <v>485</v>
       </c>
@@ -9500,7 +9487,7 @@
         <v>30.188679245283002</v>
       </c>
     </row>
-    <row r="308" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
         <v>485</v>
       </c>
@@ -9523,7 +9510,7 @@
         <v>31.746031746031701</v>
       </c>
     </row>
-    <row r="309" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
         <v>485</v>
       </c>
@@ -9546,7 +9533,7 @@
         <v>23.076923076922998</v>
       </c>
     </row>
-    <row r="310" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
         <v>487</v>
       </c>
@@ -9554,7 +9541,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="311" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
         <v>489</v>
       </c>
@@ -9562,7 +9549,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="312" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
         <v>21</v>
       </c>
@@ -9585,7 +9572,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="313" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
         <v>80</v>
       </c>
@@ -9608,7 +9595,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="314" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
         <v>31</v>
       </c>
@@ -9631,7 +9618,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="315" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
         <v>86</v>
       </c>
@@ -9654,7 +9641,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="316" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
         <v>498</v>
       </c>
@@ -9662,7 +9649,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="317" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
         <v>500</v>
       </c>
@@ -9685,7 +9672,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="318" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
         <v>500</v>
       </c>
@@ -9708,7 +9695,7 @@
         <v>41.379310344827502</v>
       </c>
     </row>
-    <row r="319" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
         <v>500</v>
       </c>
@@ -9731,7 +9718,7 @@
         <v>32.258064516128997</v>
       </c>
     </row>
-    <row r="320" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
         <v>505</v>
       </c>
@@ -9754,7 +9741,7 @@
         <v>12.1212121212121</v>
       </c>
     </row>
-    <row r="321" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
         <v>505</v>
       </c>
@@ -9777,7 +9764,7 @@
         <v>46.6666666666666</v>
       </c>
     </row>
-    <row r="322" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
         <v>505</v>
       </c>
@@ -9800,7 +9787,7 @@
         <v>28.571428571428498</v>
       </c>
     </row>
-    <row r="323" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
         <v>69</v>
       </c>
@@ -9823,7 +9810,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="324" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
         <v>49</v>
       </c>
@@ -9846,7 +9833,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="325" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
         <v>49</v>
       </c>
@@ -9869,7 +9856,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="326" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
         <v>49</v>
       </c>
@@ -9892,7 +9879,7 @@
         <v>22.2222222222222</v>
       </c>
     </row>
-    <row r="327" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
         <v>49</v>
       </c>
@@ -9915,7 +9902,7 @@
         <v>19.354838709677399</v>
       </c>
     </row>
-    <row r="328" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
         <v>90</v>
       </c>
@@ -9938,7 +9925,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="329" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
         <v>82</v>
       </c>
@@ -9961,7 +9948,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="330" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
         <v>515</v>
       </c>
@@ -9969,7 +9956,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="331" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
         <v>517</v>
       </c>
@@ -9977,7 +9964,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="332" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
         <v>519</v>
       </c>
@@ -9985,7 +9972,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="333" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
         <v>521</v>
       </c>
@@ -9993,7 +9980,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="334" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
         <v>523</v>
       </c>
@@ -10001,7 +9988,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="335" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
         <v>525</v>
       </c>
@@ -10009,7 +9996,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="336" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
         <v>527</v>
       </c>
@@ -10017,7 +10004,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="337" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A337" t="s">
         <v>529</v>
       </c>
@@ -10025,7 +10012,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="338" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
         <v>531</v>
       </c>
@@ -10033,7 +10020,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="339" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
         <v>533</v>
       </c>
@@ -10041,7 +10028,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="340" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
         <v>535</v>
       </c>
@@ -10049,7 +10036,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="341" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
         <v>96</v>
       </c>
@@ -10072,7 +10059,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="342" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
         <v>96</v>
       </c>
@@ -10095,7 +10082,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="343" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
         <v>539</v>
       </c>
@@ -10103,7 +10090,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="344" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
         <v>541</v>
       </c>
@@ -10111,7 +10098,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="345" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
         <v>97</v>
       </c>
@@ -10134,7 +10121,7 @@
         <v>30.303030303030202</v>
       </c>
     </row>
-    <row r="346" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
         <v>97</v>
       </c>
@@ -10157,7 +10144,7 @@
         <v>26.6666666666666</v>
       </c>
     </row>
-    <row r="347" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
         <v>97</v>
       </c>
@@ -10180,7 +10167,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="348" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
         <v>60</v>
       </c>
@@ -10203,7 +10190,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="349" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A349" t="s">
         <v>22</v>
       </c>
@@ -10226,7 +10213,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="350" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A350" t="s">
         <v>56</v>
       </c>
@@ -10249,7 +10236,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="351" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
         <v>56</v>
       </c>
@@ -10272,7 +10259,7 @@
         <v>10.5263157894736</v>
       </c>
     </row>
-    <row r="352" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
         <v>56</v>
       </c>
@@ -10295,7 +10282,7 @@
         <v>14.285714285714199</v>
       </c>
     </row>
-    <row r="353" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
         <v>56</v>
       </c>
@@ -10318,7 +10305,7 @@
         <v>18.181818181818102</v>
       </c>
     </row>
-    <row r="354" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
         <v>56</v>
       </c>
@@ -10341,7 +10328,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="355" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
         <v>56</v>
       </c>
@@ -10364,7 +10351,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="356" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
         <v>56</v>
       </c>
@@ -10387,7 +10374,7 @@
         <v>19.047619047619001</v>
       </c>
     </row>
-    <row r="357" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
         <v>56</v>
       </c>
@@ -10410,7 +10397,7 @@
         <v>11.764705882352899</v>
       </c>
     </row>
-    <row r="358" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
         <v>56</v>
       </c>
@@ -10433,7 +10420,7 @@
         <v>18.75</v>
       </c>
     </row>
-    <row r="359" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A359" t="s">
         <v>12</v>
       </c>
@@ -10456,7 +10443,7 @@
         <v>8.3333333333333197</v>
       </c>
     </row>
-    <row r="360" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A360" t="s">
         <v>12</v>
       </c>
@@ -10479,7 +10466,7 @@
         <v>12.1212121212121</v>
       </c>
     </row>
-    <row r="361" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
         <v>12</v>
       </c>
@@ -10502,7 +10489,7 @@
         <v>29.629629629629601</v>
       </c>
     </row>
-    <row r="362" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
         <v>12</v>
       </c>
@@ -10525,7 +10512,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="363" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A363" t="s">
         <v>12</v>
       </c>
@@ -10548,7 +10535,7 @@
         <v>18.181818181818102</v>
       </c>
     </row>
-    <row r="364" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
         <v>12</v>
       </c>
@@ -10571,7 +10558,7 @@
         <v>21.6216216216216</v>
       </c>
     </row>
-    <row r="365" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A365" t="s">
         <v>550</v>
       </c>
@@ -10594,7 +10581,7 @@
         <v>22.2222222222222</v>
       </c>
     </row>
-    <row r="366" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A366" t="s">
         <v>13</v>
       </c>
@@ -10617,7 +10604,7 @@
         <v>17.391304347826001</v>
       </c>
     </row>
-    <row r="367" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A367" t="s">
         <v>13</v>
       </c>
@@ -10640,7 +10627,7 @@
         <v>18.75</v>
       </c>
     </row>
-    <row r="368" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A368" t="s">
         <v>13</v>
       </c>
@@ -10663,7 +10650,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="369" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
         <v>13</v>
       </c>
@@ -10686,7 +10673,7 @@
         <v>29.629629629629601</v>
       </c>
     </row>
-    <row r="370" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A370" t="s">
         <v>13</v>
       </c>
@@ -10709,7 +10696,7 @@
         <v>27.272727272727199</v>
       </c>
     </row>
-    <row r="371" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A371" t="s">
         <v>13</v>
       </c>
@@ -10732,7 +10719,7 @@
         <v>21.818181818181799</v>
       </c>
     </row>
-    <row r="372" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A372" t="s">
         <v>13</v>
       </c>
@@ -10755,7 +10742,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="373" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A373" t="s">
         <v>13</v>
       </c>
@@ -10778,7 +10765,7 @@
         <v>19.047619047619001</v>
       </c>
     </row>
-    <row r="374" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A374" t="s">
         <v>13</v>
       </c>
@@ -10801,7 +10788,7 @@
         <v>22.2222222222222</v>
       </c>
     </row>
-    <row r="375" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A375" t="s">
         <v>75</v>
       </c>
@@ -10824,7 +10811,7 @@
         <v>26.086956521739101</v>
       </c>
     </row>
-    <row r="376" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A376" t="s">
         <v>75</v>
       </c>
@@ -10847,7 +10834,7 @@
         <v>18.181818181818102</v>
       </c>
     </row>
-    <row r="377" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A377" t="s">
         <v>75</v>
       </c>
@@ -10870,7 +10857,7 @@
         <v>19.354838709677399</v>
       </c>
     </row>
-    <row r="378" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A378" t="s">
         <v>75</v>
       </c>
@@ -10893,7 +10880,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="379" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A379" t="s">
         <v>75</v>
       </c>
@@ -10916,7 +10903,7 @@
         <v>19.047619047619001</v>
       </c>
     </row>
-    <row r="380" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A380" t="s">
         <v>75</v>
       </c>
@@ -10939,7 +10926,7 @@
         <v>18.518518518518501</v>
       </c>
     </row>
-    <row r="381" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A381" t="s">
         <v>75</v>
       </c>
@@ -10962,7 +10949,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="382" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A382" t="s">
         <v>75</v>
       </c>
@@ -10985,7 +10972,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="383" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A383" t="s">
         <v>75</v>
       </c>
@@ -11008,7 +10995,7 @@
         <v>17.1428571428571</v>
       </c>
     </row>
-    <row r="384" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A384" t="s">
         <v>28</v>
       </c>
@@ -11031,7 +11018,7 @@
         <v>35.294117647058798</v>
       </c>
     </row>
-    <row r="385" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A385" t="s">
         <v>28</v>
       </c>
@@ -11054,7 +11041,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="386" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A386" t="s">
         <v>558</v>
       </c>
@@ -11062,7 +11049,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="387" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A387" t="s">
         <v>560</v>
       </c>
@@ -11070,7 +11057,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="388" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A388" t="s">
         <v>562</v>
       </c>
@@ -11093,7 +11080,7 @@
         <v>6.8965517241379297</v>
       </c>
     </row>
-    <row r="389" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A389" t="s">
         <v>562</v>
       </c>
@@ -11116,7 +11103,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="390" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A390" t="s">
         <v>562</v>
       </c>
@@ -11139,7 +11126,7 @@
         <v>32.558139534883701</v>
       </c>
     </row>
-    <row r="391" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A391" t="s">
         <v>61</v>
       </c>
@@ -11162,7 +11149,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="392" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A392" t="s">
         <v>61</v>
       </c>
@@ -11185,7 +11172,7 @@
         <v>23.2558139534883</v>
       </c>
     </row>
-    <row r="393" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A393" t="s">
         <v>566</v>
       </c>
@@ -11208,7 +11195,7 @@
         <v>10.1694915254237</v>
       </c>
     </row>
-    <row r="394" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A394" t="s">
         <v>566</v>
       </c>
@@ -11231,7 +11218,7 @@
         <v>34.567901234567898</v>
       </c>
     </row>
-    <row r="395" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A395" t="s">
         <v>566</v>
       </c>
@@ -11254,7 +11241,7 @@
         <v>27.272727272727199</v>
       </c>
     </row>
-    <row r="396" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A396" t="s">
         <v>568</v>
       </c>
@@ -11262,7 +11249,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="397" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A397" t="s">
         <v>570</v>
       </c>
@@ -11270,7 +11257,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="398" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A398" t="s">
         <v>572</v>
       </c>
@@ -11278,7 +11265,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="399" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A399" t="s">
         <v>574</v>
       </c>
@@ -11286,7 +11273,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="400" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A400" t="s">
         <v>576</v>
       </c>
@@ -11294,7 +11281,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="401" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A401" t="s">
         <v>578</v>
       </c>
@@ -11302,7 +11289,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="402" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A402" t="s">
         <v>580</v>
       </c>
@@ -11310,7 +11297,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="403" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A403" t="s">
         <v>78</v>
       </c>
@@ -11333,7 +11320,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="404" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A404" t="s">
         <v>582</v>
       </c>
@@ -11341,7 +11328,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="405" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A405" t="s">
         <v>584</v>
       </c>
@@ -11364,7 +11351,7 @@
         <v>9.0909090909090899</v>
       </c>
     </row>
-    <row r="406" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A406" t="s">
         <v>586</v>
       </c>
@@ -11372,7 +11359,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="407" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A407" t="s">
         <v>3</v>
       </c>
@@ -11395,7 +11382,7 @@
         <v>28.571428571428498</v>
       </c>
     </row>
-    <row r="408" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A408" t="s">
         <v>3</v>
       </c>
@@ -11418,7 +11405,7 @@
         <v>28.571428571428498</v>
       </c>
     </row>
-    <row r="409" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A409" t="s">
         <v>590</v>
       </c>
@@ -11426,7 +11413,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="410" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A410" t="s">
         <v>592</v>
       </c>
@@ -11449,7 +11436,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="411" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A411" t="s">
         <v>595</v>
       </c>
@@ -11457,7 +11444,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="412" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A412" t="s">
         <v>597</v>
       </c>
@@ -11465,7 +11452,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="413" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A413" t="s">
         <v>599</v>
       </c>
@@ -11473,7 +11460,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="414" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A414" t="s">
         <v>601</v>
       </c>
@@ -11496,7 +11483,7 @@
         <v>33.3333333333333</v>
       </c>
     </row>
-    <row r="415" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A415" t="s">
         <v>63</v>
       </c>
@@ -11519,7 +11506,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="416" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A416" t="s">
         <v>604</v>
       </c>
@@ -11542,7 +11529,7 @@
         <v>27.7777777777777</v>
       </c>
     </row>
-    <row r="417" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A417" t="s">
         <v>66</v>
       </c>
@@ -11565,7 +11552,7 @@
         <v>28.571428571428498</v>
       </c>
     </row>
-    <row r="418" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A418" t="s">
         <v>66</v>
       </c>
@@ -11588,7 +11575,7 @@
         <v>72.727272727272705</v>
       </c>
     </row>
-    <row r="419" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A419" t="s">
         <v>66</v>
       </c>
@@ -11611,7 +11598,7 @@
         <v>31.034482758620602</v>
       </c>
     </row>
-    <row r="420" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A420" t="s">
         <v>66</v>
       </c>
@@ -11634,7 +11621,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="421" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A421" t="s">
         <v>66</v>
       </c>
@@ -11657,7 +11644,7 @@
         <v>20.8333333333333</v>
       </c>
     </row>
-    <row r="422" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A422" t="s">
         <v>66</v>
       </c>
@@ -11680,7 +11667,7 @@
         <v>28.571428571428498</v>
       </c>
     </row>
-    <row r="423" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A423" t="s">
         <v>66</v>
       </c>
@@ -11703,7 +11690,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="424" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A424" t="s">
         <v>66</v>
       </c>
@@ -11726,7 +11713,7 @@
         <v>22.727272727272702</v>
       </c>
     </row>
-    <row r="425" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A425" t="s">
         <v>66</v>
       </c>
@@ -11749,7 +11736,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="426" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A426" t="s">
         <v>66</v>
       </c>
@@ -11772,7 +11759,7 @@
         <v>25.806451612903199</v>
       </c>
     </row>
-    <row r="427" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A427" t="s">
         <v>66</v>
       </c>
@@ -11795,7 +11782,7 @@
         <v>31.25</v>
       </c>
     </row>
-    <row r="428" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A428" t="s">
         <v>608</v>
       </c>
@@ -11818,7 +11805,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="429" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A429" t="s">
         <v>608</v>
       </c>
@@ -11841,7 +11828,7 @@
         <v>21.052631578947299</v>
       </c>
     </row>
-    <row r="430" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A430" t="s">
         <v>612</v>
       </c>
@@ -11849,7 +11836,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="431" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A431" t="s">
         <v>614</v>
       </c>
@@ -11857,7 +11844,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="432" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A432" t="s">
         <v>616</v>
       </c>
@@ -11880,7 +11867,7 @@
         <v>20.408163265306101</v>
       </c>
     </row>
-    <row r="433" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A433" t="s">
         <v>616</v>
       </c>
@@ -11903,7 +11890,7 @@
         <v>18.867924528301799</v>
       </c>
     </row>
-    <row r="434" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A434" t="s">
         <v>618</v>
       </c>
@@ -11926,7 +11913,7 @@
         <v>14.814814814814801</v>
       </c>
     </row>
-    <row r="435" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A435" t="s">
         <v>621</v>
       </c>
@@ -11934,7 +11921,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="436" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A436" t="s">
         <v>623</v>
       </c>
@@ -11957,7 +11944,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="437" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A437" t="s">
         <v>623</v>
       </c>
@@ -11980,7 +11967,7 @@
         <v>51.851851851851798</v>
       </c>
     </row>
-    <row r="438" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A438" t="s">
         <v>23</v>
       </c>
@@ -12003,7 +11990,7 @@
         <v>10.5263157894736</v>
       </c>
     </row>
-    <row r="439" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A439" t="s">
         <v>23</v>
       </c>
@@ -12026,7 +12013,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="440" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A440" t="s">
         <v>626</v>
       </c>
@@ -12049,7 +12036,7 @@
         <v>40.909090909090899</v>
       </c>
     </row>
-    <row r="441" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A441" t="s">
         <v>626</v>
       </c>
@@ -12072,7 +12059,7 @@
         <v>55.172413793103402</v>
       </c>
     </row>
-    <row r="442" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A442" t="s">
         <v>628</v>
       </c>
@@ -12080,7 +12067,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="443" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A443" t="s">
         <v>630</v>
       </c>
@@ -12088,7 +12075,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="444" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A444" t="s">
         <v>34</v>
       </c>
@@ -12111,7 +12098,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="445" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A445" t="s">
         <v>634</v>
       </c>
@@ -12119,7 +12106,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="446" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A446" t="s">
         <v>35</v>
       </c>
@@ -12142,7 +12129,7 @@
         <v>37.5</v>
       </c>
     </row>
-    <row r="447" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A447" t="s">
         <v>638</v>
       </c>
@@ -12150,7 +12137,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="448" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A448" t="s">
         <v>83</v>
       </c>
@@ -12173,7 +12160,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="449" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A449" t="s">
         <v>642</v>
       </c>
@@ -12181,7 +12168,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="450" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A450" t="s">
         <v>46</v>
       </c>
@@ -12204,7 +12191,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="451" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A451" t="s">
         <v>646</v>
       </c>
@@ -12212,7 +12199,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="452" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A452" t="s">
         <v>73</v>
       </c>
@@ -12235,7 +12222,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="453" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A453" t="s">
         <v>650</v>
       </c>
@@ -12243,7 +12230,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="454" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A454" t="s">
         <v>652</v>
       </c>
@@ -12251,7 +12238,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="455" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A455" t="s">
         <v>654</v>
       </c>
@@ -12274,7 +12261,7 @@
         <v>29.268292682926798</v>
       </c>
     </row>
-    <row r="456" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A456" t="s">
         <v>656</v>
       </c>
@@ -12297,7 +12284,7 @@
         <v>22.2222222222222</v>
       </c>
     </row>
-    <row r="457" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A457" t="s">
         <v>656</v>
       </c>
@@ -12320,7 +12307,7 @@
         <v>26.315789473684202</v>
       </c>
     </row>
-    <row r="458" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A458" t="s">
         <v>19</v>
       </c>
@@ -12343,7 +12330,7 @@
         <v>18.604651162790699</v>
       </c>
     </row>
-    <row r="459" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A459" t="s">
         <v>19</v>
       </c>
@@ -12366,7 +12353,7 @@
         <v>20.5128205128205</v>
       </c>
     </row>
-    <row r="460" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A460" t="s">
         <v>19</v>
       </c>
@@ -12389,7 +12376,7 @@
         <v>20.689655172413701</v>
       </c>
     </row>
-    <row r="461" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A461" t="s">
         <v>19</v>
       </c>
@@ -12412,7 +12399,7 @@
         <v>23.529411764705799</v>
       </c>
     </row>
-    <row r="462" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A462" t="s">
         <v>20</v>
       </c>
@@ -12435,7 +12422,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="463" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A463" t="s">
         <v>20</v>
       </c>
@@ -12458,7 +12445,7 @@
         <v>28.571428571428498</v>
       </c>
     </row>
-    <row r="464" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A464" t="s">
         <v>20</v>
       </c>
@@ -12481,7 +12468,7 @@
         <v>22.857142857142801</v>
       </c>
     </row>
-    <row r="465" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A465" t="s">
         <v>20</v>
       </c>
@@ -12504,7 +12491,7 @@
         <v>33.3333333333333</v>
       </c>
     </row>
-    <row r="466" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A466" t="s">
         <v>20</v>
       </c>
@@ -12527,7 +12514,7 @@
         <v>22.857142857142801</v>
       </c>
     </row>
-    <row r="467" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A467" t="s">
         <v>20</v>
       </c>
@@ -12550,7 +12537,7 @@
         <v>29.629629629629601</v>
       </c>
     </row>
-    <row r="468" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A468" t="s">
         <v>20</v>
       </c>
@@ -12573,7 +12560,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="469" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A469" t="s">
         <v>20</v>
       </c>
@@ -12596,7 +12583,7 @@
         <v>31.578947368421002</v>
       </c>
     </row>
-    <row r="470" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A470" t="s">
         <v>92</v>
       </c>
@@ -12619,7 +12606,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="471" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A471" t="s">
         <v>92</v>
       </c>
@@ -12642,7 +12629,7 @@
         <v>33.3333333333333</v>
       </c>
     </row>
-    <row r="472" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A472" t="s">
         <v>92</v>
       </c>
@@ -12665,7 +12652,7 @@
         <v>15.6862745098039</v>
       </c>
     </row>
-    <row r="473" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A473" t="s">
         <v>92</v>
       </c>
@@ -12688,7 +12675,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="474" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A474" t="s">
         <v>89</v>
       </c>
@@ -12711,7 +12698,7 @@
         <v>28.571428571428498</v>
       </c>
     </row>
-    <row r="475" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A475" t="s">
         <v>89</v>
       </c>
@@ -12734,7 +12721,7 @@
         <v>19.354838709677399</v>
       </c>
     </row>
-    <row r="476" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A476" t="s">
         <v>89</v>
       </c>
@@ -12757,7 +12744,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="477" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A477" t="s">
         <v>89</v>
       </c>
@@ -12780,7 +12767,7 @@
         <v>29.411764705882302</v>
       </c>
     </row>
-    <row r="478" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A478" t="s">
         <v>89</v>
       </c>
@@ -12803,7 +12790,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="479" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A479" t="s">
         <v>89</v>
       </c>
@@ -12826,7 +12813,7 @@
         <v>21.6216216216216</v>
       </c>
     </row>
-    <row r="480" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A480" t="s">
         <v>89</v>
       </c>
@@ -12849,7 +12836,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="481" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A481" t="s">
         <v>89</v>
       </c>
@@ -12872,7 +12859,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="482" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A482" t="s">
         <v>36</v>
       </c>
@@ -12895,7 +12882,7 @@
         <v>28.571428571428498</v>
       </c>
     </row>
-    <row r="483" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A483" t="s">
         <v>36</v>
       </c>
@@ -12918,7 +12905,7 @@
         <v>19.354838709677399</v>
       </c>
     </row>
-    <row r="484" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A484" t="s">
         <v>36</v>
       </c>
@@ -12941,7 +12928,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="485" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A485" t="s">
         <v>36</v>
       </c>
@@ -12964,7 +12951,7 @@
         <v>29.411764705882302</v>
       </c>
     </row>
-    <row r="486" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A486" t="s">
         <v>36</v>
       </c>
@@ -12987,7 +12974,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="487" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A487" t="s">
         <v>36</v>
       </c>
@@ -13010,7 +12997,7 @@
         <v>21.6216216216216</v>
       </c>
     </row>
-    <row r="488" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A488" t="s">
         <v>36</v>
       </c>
@@ -13033,7 +13020,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="489" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A489" t="s">
         <v>36</v>
       </c>
@@ -13056,7 +13043,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="490" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A490" t="s">
         <v>24</v>
       </c>
@@ -13079,7 +13066,7 @@
         <v>21.739130434782599</v>
       </c>
     </row>
-    <row r="491" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A491" t="s">
         <v>24</v>
       </c>
@@ -13102,7 +13089,7 @@
         <v>33.3333333333333</v>
       </c>
     </row>
-    <row r="492" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A492" t="s">
         <v>24</v>
       </c>
@@ -13125,7 +13112,7 @@
         <v>23.529411764705799</v>
       </c>
     </row>
-    <row r="493" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A493" t="s">
         <v>24</v>
       </c>
@@ -13148,7 +13135,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="494" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A494" t="s">
         <v>24</v>
       </c>
@@ -13171,7 +13158,7 @@
         <v>23.529411764705799</v>
       </c>
     </row>
-    <row r="495" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A495" t="s">
         <v>24</v>
       </c>
@@ -13194,7 +13181,7 @@
         <v>30.769230769230699</v>
       </c>
     </row>
-    <row r="496" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A496" t="s">
         <v>24</v>
       </c>
@@ -13217,7 +13204,7 @@
         <v>33.3333333333333</v>
       </c>
     </row>
-    <row r="497" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A497" t="s">
         <v>24</v>
       </c>
@@ -13240,7 +13227,7 @@
         <v>27.586206896551701</v>
       </c>
     </row>
-    <row r="498" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A498" t="s">
         <v>24</v>
       </c>
@@ -13263,7 +13250,7 @@
         <v>27.027027027027</v>
       </c>
     </row>
-    <row r="499" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A499" t="s">
         <v>27</v>
       </c>
@@ -13286,7 +13273,7 @@
         <v>7.4074074074074003</v>
       </c>
     </row>
-    <row r="500" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A500" t="s">
         <v>27</v>
       </c>
@@ -13309,7 +13296,7 @@
         <v>19.047619047619001</v>
       </c>
     </row>
-    <row r="501" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A501" t="s">
         <v>27</v>
       </c>
@@ -13332,7 +13319,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="502" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A502" t="s">
         <v>27</v>
       </c>
@@ -13355,7 +13342,7 @@
         <v>26.086956521739101</v>
       </c>
     </row>
-    <row r="503" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A503" t="s">
         <v>27</v>
       </c>
@@ -13378,7 +13365,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="504" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A504" t="s">
         <v>27</v>
       </c>
@@ -13401,7 +13388,7 @@
         <v>7.6923076923076898</v>
       </c>
     </row>
-    <row r="505" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A505" t="s">
         <v>10</v>
       </c>
@@ -13424,7 +13411,7 @@
         <v>26.6666666666666</v>
       </c>
     </row>
-    <row r="506" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A506" t="s">
         <v>10</v>
       </c>
@@ -13447,7 +13434,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="507" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A507" t="s">
         <v>674</v>
       </c>
@@ -13470,7 +13457,7 @@
         <v>59.259259259259203</v>
       </c>
     </row>
-    <row r="508" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A508" t="s">
         <v>9</v>
       </c>
@@ -13493,7 +13480,7 @@
         <v>13.953488372093</v>
       </c>
     </row>
-    <row r="509" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A509" t="s">
         <v>9</v>
       </c>
@@ -13516,7 +13503,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="510" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A510" t="s">
         <v>9</v>
       </c>
@@ -13539,7 +13526,7 @@
         <v>26.6666666666666</v>
       </c>
     </row>
-    <row r="511" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A511" t="s">
         <v>33</v>
       </c>
@@ -13562,7 +13549,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="512" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A512" t="s">
         <v>65</v>
       </c>
@@ -13585,7 +13572,7 @@
         <v>64.705882352941103</v>
       </c>
     </row>
-    <row r="513" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A513" t="s">
         <v>682</v>
       </c>
@@ -13593,7 +13580,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="514" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A514" t="s">
         <v>684</v>
       </c>
@@ -13616,7 +13603,7 @@
         <v>51.428571428571402</v>
       </c>
     </row>
-    <row r="515" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A515" t="s">
         <v>687</v>
       </c>
@@ -13624,7 +13611,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="516" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A516" t="s">
         <v>689</v>
       </c>
@@ -13632,7 +13619,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="517" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A517" t="s">
         <v>691</v>
       </c>
@@ -13640,7 +13627,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="518" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A518" t="s">
         <v>693</v>
       </c>
@@ -13648,7 +13635,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="519" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A519" t="s">
         <v>695</v>
       </c>
@@ -13656,7 +13643,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="520" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A520" t="s">
         <v>5</v>
       </c>
@@ -13679,7 +13666,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="521" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A521" t="s">
         <v>5</v>
       </c>
@@ -13702,7 +13689,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="522" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A522" t="s">
         <v>700</v>
       </c>
@@ -13725,7 +13712,7 @@
         <v>22.2222222222222</v>
       </c>
     </row>
-    <row r="523" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A523" t="s">
         <v>700</v>
       </c>
@@ -13748,7 +13735,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="524" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A524" t="s">
         <v>700</v>
       </c>
@@ -13771,7 +13758,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="525" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A525" t="s">
         <v>702</v>
       </c>
@@ -13794,7 +13781,7 @@
         <v>23.076923076922998</v>
       </c>
     </row>
-    <row r="526" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A526" t="s">
         <v>702</v>
       </c>
@@ -13817,7 +13804,7 @@
         <v>16.6666666666666</v>
       </c>
     </row>
-    <row r="527" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A527" t="s">
         <v>704</v>
       </c>
@@ -13840,7 +13827,7 @@
         <v>28.571428571428498</v>
       </c>
     </row>
-    <row r="528" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A528" t="s">
         <v>706</v>
       </c>
@@ -13848,7 +13835,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="529" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A529" t="s">
         <v>708</v>
       </c>
@@ -13856,7 +13843,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="530" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A530" t="s">
         <v>710</v>
       </c>
@@ -13864,7 +13851,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="531" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B531">
         <v>25155</v>
       </c>
@@ -13872,7 +13859,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="532" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B532">
         <v>29389</v>
       </c>
@@ -13880,7 +13867,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="533" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B533">
         <v>33878</v>
       </c>
@@ -13888,7 +13875,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="534" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B534">
         <v>28456</v>
       </c>
@@ -13896,7 +13883,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="535" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B535">
         <v>28455</v>
       </c>
@@ -13904,7 +13891,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="536" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B536">
         <v>29381</v>
       </c>
@@ -13912,7 +13899,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="537" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B537">
         <v>8600</v>
       </c>
@@ -13920,7 +13907,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="538" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B538">
         <v>3414</v>
       </c>
@@ -13928,7 +13915,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="539" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B539">
         <v>31795</v>
       </c>
@@ -13936,7 +13923,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="540" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B540">
         <v>11743</v>
       </c>
@@ -13944,7 +13931,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="541" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B541">
         <v>6425</v>
       </c>
@@ -13952,7 +13939,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="542" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B542">
         <v>29897</v>
       </c>
@@ -13960,7 +13947,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="543" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B543">
         <v>34791</v>
       </c>
@@ -13968,7 +13955,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="544" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B544">
         <v>11623</v>
       </c>
@@ -13976,7 +13963,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="545" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="545" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B545">
         <v>32987</v>
       </c>
@@ -13984,7 +13971,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="546" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="546" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B546">
         <v>2794</v>
       </c>
@@ -13992,7 +13979,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="547" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="547" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B547">
         <v>2371</v>
       </c>
@@ -14000,7 +13987,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="548" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="548" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B548">
         <v>4922</v>
       </c>
@@ -14008,7 +13995,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="549" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="549" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B549">
         <v>10537</v>
       </c>
@@ -14016,7 +14003,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="550" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="550" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B550">
         <v>11811</v>
       </c>
@@ -14024,7 +14011,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="551" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="551" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B551">
         <v>28947</v>
       </c>
@@ -14032,7 +14019,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="552" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="552" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B552">
         <v>3219</v>
       </c>
@@ -14040,7 +14027,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="553" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="553" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B553">
         <v>11649</v>
       </c>
@@ -14048,7 +14035,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="554" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="554" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B554">
         <v>4819</v>
       </c>
@@ -14056,7 +14043,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="555" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="555" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B555">
         <v>7825</v>
       </c>
@@ -14064,7 +14051,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="556" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="556" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B556">
         <v>6363</v>
       </c>
@@ -14072,7 +14059,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="557" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="557" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B557">
         <v>2396</v>
       </c>
@@ -14080,7 +14067,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="558" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="558" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B558">
         <v>7325</v>
       </c>
@@ -14088,7 +14075,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="559" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="559" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B559">
         <v>5649</v>
       </c>
@@ -14096,7 +14083,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="560" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="560" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B560">
         <v>1541</v>
       </c>
@@ -14104,7 +14091,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="561" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="561" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B561">
         <v>7154</v>
       </c>
@@ -14112,7 +14099,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="562" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="562" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B562">
         <v>701</v>
       </c>
@@ -14120,7 +14107,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="563" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="563" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B563">
         <v>11158</v>
       </c>
@@ -14128,7 +14115,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="564" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="564" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B564">
         <v>7080</v>
       </c>
@@ -14136,7 +14123,7 @@
         <v>744</v>
       </c>
     </row>
-    <row r="565" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="565" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B565">
         <v>4799</v>
       </c>
@@ -14144,7 +14131,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="566" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="566" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B566">
         <v>11787</v>
       </c>
@@ -14152,7 +14139,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="567" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="567" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B567">
         <v>7674</v>
       </c>
@@ -14160,7 +14147,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="568" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="568" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B568">
         <v>7675</v>
       </c>
@@ -14168,7 +14155,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="569" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="569" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B569">
         <v>6366</v>
       </c>
@@ -14176,7 +14163,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="570" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="570" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B570">
         <v>4761</v>
       </c>
@@ -14184,7 +14171,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="571" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="571" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B571">
         <v>11713</v>
       </c>
@@ -14192,7 +14179,7 @@
         <v>751</v>
       </c>
     </row>
-    <row r="572" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="572" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B572">
         <v>11372</v>
       </c>
@@ -14200,7 +14187,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="573" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="573" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B573">
         <v>2544</v>
       </c>
@@ -14208,7 +14195,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="574" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="574" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B574">
         <v>4978</v>
       </c>
@@ -14216,7 +14203,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="575" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="575" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B575">
         <v>3032</v>
       </c>
@@ -14224,7 +14211,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="576" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="576" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B576">
         <v>31796</v>
       </c>
@@ -14232,7 +14219,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="577" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="577" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B577">
         <v>32448</v>
       </c>
@@ -14240,7 +14227,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="578" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="578" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B578">
         <v>10418</v>
       </c>
@@ -14248,7 +14235,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="579" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="579" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B579">
         <v>21</v>
       </c>
@@ -14256,7 +14243,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="580" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="580" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B580">
         <v>5183</v>
       </c>
@@ -14264,7 +14251,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="581" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="581" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B581">
         <v>4472</v>
       </c>
@@ -14272,7 +14259,7 @@
         <v>761</v>
       </c>
     </row>
-    <row r="582" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="582" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B582">
         <v>23568</v>
       </c>
@@ -14280,7 +14267,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="583" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="583" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B583">
         <v>276</v>
       </c>
@@ -14288,7 +14275,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="584" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="584" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B584">
         <v>11004</v>
       </c>
@@ -14296,7 +14283,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="585" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="585" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B585">
         <v>2741</v>
       </c>
@@ -14304,7 +14291,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="586" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="586" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B586">
         <v>27784</v>
       </c>
@@ -14312,7 +14299,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="587" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="587" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B587">
         <v>28578</v>
       </c>
@@ -14320,7 +14307,7 @@
         <v>767</v>
       </c>
     </row>
-    <row r="588" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="588" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B588">
         <v>24203</v>
       </c>
@@ -14328,7 +14315,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="589" spans="2:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="589" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B589">
         <v>4717</v>
       </c>
@@ -14338,9 +14325,9 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:G589" xr:uid="{556460DC-71F1-43FF-BD31-36D25365B781}">
-    <filterColumn colId="4">
+    <filterColumn colId="1">
       <filters>
-        <filter val="Sudbury Operations Mines Mill - Onaping Area"/>
+        <filter val="3598"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/data/Mappings/mapping_npri.xlsx
+++ b/data/Mappings/mapping_npri.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mp_ma\OneDrive - polymtl\POST_DOC\CODE\metallican_db\data\Mappings\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://polymtlca-my.sharepoint.com/personal/marin_pellan_polymtl_ca/Documents/POST_DOC/CODE/metallican_db/data/Mappings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79931472-8B2F-4982-8306-AF8D7544F4B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="30" documentId="13_ncr:1_{79931472-8B2F-4982-8306-AF8D7544F4B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4732ECFD-CD28-4C63-8A5D-652DACEDACE3}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="mapping" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1631" uniqueCount="770">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1635" uniqueCount="770">
   <si>
     <t>npri_id</t>
   </si>
@@ -2355,12 +2355,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -2375,8 +2381,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2392,6 +2399,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2657,11 +2668,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B104"/>
+  <dimension ref="A1:B108"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.54296875" customWidth="1"/>
-    <col min="2" max="2" width="17.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
@@ -3494,6 +3505,38 @@
       </c>
       <c r="B104" t="s">
         <v>8</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A105" s="1">
+        <v>99</v>
+      </c>
+      <c r="B105" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A106" s="1">
+        <v>29389</v>
+      </c>
+      <c r="B106" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A107" s="1">
+        <v>8600</v>
+      </c>
+      <c r="B107" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A108" s="1">
+        <v>32238</v>
+      </c>
+      <c r="B108" t="s">
+        <v>684</v>
       </c>
     </row>
   </sheetData>
@@ -3767,26 +3810,26 @@
         <v>29.629629629629601</v>
       </c>
     </row>
-    <row r="13" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
+    <row r="13" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="1">
         <v>99</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="1">
         <v>1035.5</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="1">
         <v>85.714285714285694</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="1">
         <v>52.173913043478201</v>
       </c>
     </row>
@@ -4228,7 +4271,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>44</v>
       </c>
@@ -6208,7 +6251,7 @@
         <v>23.8095238095238</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>93</v>
       </c>
@@ -6346,7 +6389,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>15</v>
       </c>
@@ -9464,7 +9507,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="307" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
         <v>485</v>
       </c>
@@ -13580,7 +13623,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="514" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="514" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A514" t="s">
         <v>684</v>
       </c>
@@ -13643,7 +13686,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="520" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="520" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A520" t="s">
         <v>5</v>
       </c>
@@ -13666,7 +13709,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="521" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="521" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A521" t="s">
         <v>5</v>
       </c>
@@ -13835,7 +13878,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="529" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="529" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A529" t="s">
         <v>708</v>
       </c>
@@ -13859,11 +13902,11 @@
         <v>712</v>
       </c>
     </row>
-    <row r="532" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B532">
+    <row r="532" spans="1:5" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B532" s="1">
         <v>29389</v>
       </c>
-      <c r="E532" t="s">
+      <c r="E532" s="1" t="s">
         <v>713</v>
       </c>
     </row>
@@ -13899,11 +13942,11 @@
         <v>717</v>
       </c>
     </row>
-    <row r="537" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B537">
+    <row r="537" spans="1:5" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B537" s="1">
         <v>8600</v>
       </c>
-      <c r="E537" t="s">
+      <c r="E537" s="1" t="s">
         <v>390</v>
       </c>
     </row>
@@ -14325,9 +14368,11 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:G589" xr:uid="{556460DC-71F1-43FF-BD31-36D25365B781}">
-    <filterColumn colId="1">
+    <filterColumn colId="3">
       <filters>
-        <filter val="3598"/>
+        <filter val="Eagle (Dublin Gulch)"/>
+        <filter val="Eagle River"/>
+        <filter val="Eagle's Nest"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/data/Mappings/mapping_npri.xlsx
+++ b/data/Mappings/mapping_npri.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://polymtlca-my.sharepoint.com/personal/marin_pellan_polymtl_ca/Documents/POST_DOC/CODE/metallican_db/data/Mappings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="30" documentId="13_ncr:1_{79931472-8B2F-4982-8306-AF8D7544F4B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4732ECFD-CD28-4C63-8A5D-652DACEDACE3}"/>
+  <xr:revisionPtr revIDLastSave="69" documentId="13_ncr:1_{79931472-8B2F-4982-8306-AF8D7544F4B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{79F3E67D-279D-4663-B2A3-B2BF2D31F971}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-705" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="mapping" sheetId="1" r:id="rId1"/>
@@ -18,12 +18,23 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">LT!$A$1:$G$589</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">mapping!$A$1:$B$104</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">mapping!$A$1:$B$108</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -2355,7 +2366,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2365,6 +2376,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2381,9 +2398,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2684,10 +2703,10 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2">
+      <c r="A2" s="1">
         <v>444</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>36</v>
       </c>
     </row>
@@ -2764,10 +2783,10 @@
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A12">
+      <c r="A12" s="1">
         <v>1467</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="1" t="s">
         <v>36</v>
       </c>
     </row>
@@ -3252,18 +3271,18 @@
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A73">
+      <c r="A73" s="1">
         <v>10203</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B73" s="1" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A74">
+      <c r="A74" s="1">
         <v>10204</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B74" s="1" t="s">
         <v>89</v>
       </c>
     </row>
@@ -3540,7 +3559,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B104" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <autoFilter ref="A1:B108" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B104">
       <sortCondition ref="A1:A104"/>
     </sortState>
@@ -7285,16 +7304,16 @@
       <c r="C193">
         <v>31.52</v>
       </c>
-      <c r="D193" t="s">
+      <c r="D193" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="E193" t="s">
+      <c r="E193" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="F193">
-        <v>100</v>
-      </c>
-      <c r="G193">
+      <c r="F193" s="2">
+        <v>100</v>
+      </c>
+      <c r="G193" s="2">
         <v>100</v>
       </c>
     </row>
@@ -7400,16 +7419,16 @@
       <c r="C198">
         <v>5713.75</v>
       </c>
-      <c r="D198" t="s">
+      <c r="D198" s="3" t="s">
         <v>370</v>
       </c>
-      <c r="E198" t="s">
+      <c r="E198" s="3" t="s">
         <v>357</v>
       </c>
-      <c r="F198">
+      <c r="F198" s="3">
         <v>72</v>
       </c>
-      <c r="G198">
+      <c r="G198" s="3">
         <v>70</v>
       </c>
     </row>
@@ -7469,16 +7488,16 @@
       <c r="C201">
         <v>633.39</v>
       </c>
-      <c r="D201" t="s">
+      <c r="D201" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="E201" t="s">
+      <c r="E201" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="F201">
-        <v>100</v>
-      </c>
-      <c r="G201">
+      <c r="F201" s="2">
+        <v>100</v>
+      </c>
+      <c r="G201" s="2">
         <v>100</v>
       </c>
     </row>
@@ -7538,16 +7557,16 @@
       <c r="C204">
         <v>91.11</v>
       </c>
-      <c r="D204" t="s">
+      <c r="D204" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="E204" t="s">
+      <c r="E204" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="F204">
+      <c r="F204" s="2">
         <v>50</v>
       </c>
-      <c r="G204">
+      <c r="G204" s="2">
         <v>18.518518518518501</v>
       </c>
     </row>
@@ -7653,16 +7672,16 @@
       <c r="C209">
         <v>402.62</v>
       </c>
-      <c r="D209" t="s">
+      <c r="D209" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="E209" t="s">
+      <c r="E209" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="F209">
-        <v>100</v>
-      </c>
-      <c r="G209">
+      <c r="F209" s="2">
+        <v>100</v>
+      </c>
+      <c r="G209" s="2">
         <v>100</v>
       </c>
     </row>
@@ -8309,16 +8328,16 @@
       <c r="C246">
         <v>90.16</v>
       </c>
-      <c r="D246" t="s">
+      <c r="D246" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="E246" t="s">
+      <c r="E246" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="F246">
-        <v>100</v>
-      </c>
-      <c r="G246">
+      <c r="F246" s="2">
+        <v>100</v>
+      </c>
+      <c r="G246" s="2">
         <v>100</v>
       </c>
     </row>
@@ -9692,7 +9711,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="317" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
         <v>500</v>
       </c>
@@ -9761,7 +9780,7 @@
         <v>32.258064516128997</v>
       </c>
     </row>
-    <row r="320" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
         <v>505</v>
       </c>
@@ -9853,7 +9872,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="324" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
         <v>49</v>
       </c>
@@ -10141,7 +10160,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="345" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
         <v>97</v>
       </c>
@@ -12452,16 +12471,16 @@
       <c r="C462">
         <v>106.41</v>
       </c>
-      <c r="D462" t="s">
+      <c r="D462" s="2" t="s">
         <v>663</v>
       </c>
-      <c r="E462" t="s">
+      <c r="E462" s="2" t="s">
         <v>664</v>
       </c>
-      <c r="F462">
-        <v>100</v>
-      </c>
-      <c r="G462">
+      <c r="F462" s="2">
+        <v>100</v>
+      </c>
+      <c r="G462" s="2">
         <v>100</v>
       </c>
     </row>
@@ -12705,16 +12724,16 @@
       <c r="C473">
         <v>5072.8500000000004</v>
       </c>
-      <c r="D473" t="s">
+      <c r="D473" s="2" t="s">
         <v>669</v>
       </c>
-      <c r="E473" t="s">
+      <c r="E473" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="F473">
-        <v>100</v>
-      </c>
-      <c r="G473">
+      <c r="F473" s="2">
+        <v>100</v>
+      </c>
+      <c r="G473" s="2">
         <v>100</v>
       </c>
     </row>
@@ -12774,10 +12793,10 @@
       <c r="C476">
         <v>2590.16</v>
       </c>
-      <c r="D476" t="s">
+      <c r="D476" s="2" t="s">
         <v>670</v>
       </c>
-      <c r="E476" t="s">
+      <c r="E476" s="2" t="s">
         <v>665</v>
       </c>
       <c r="F476">
@@ -12820,10 +12839,10 @@
       <c r="C478">
         <v>3692.02</v>
       </c>
-      <c r="D478" t="s">
+      <c r="D478" s="2" t="s">
         <v>670</v>
       </c>
-      <c r="E478" t="s">
+      <c r="E478" s="2" t="s">
         <v>666</v>
       </c>
       <c r="F478">
@@ -13050,16 +13069,16 @@
       <c r="C488">
         <v>209.3</v>
       </c>
-      <c r="D488" t="s">
+      <c r="D488" s="2" t="s">
         <v>670</v>
       </c>
-      <c r="E488" t="s">
+      <c r="E488" s="2" t="s">
         <v>667</v>
       </c>
-      <c r="F488">
+      <c r="F488" s="2">
         <v>83.3333333333333</v>
       </c>
-      <c r="G488">
+      <c r="G488" s="2">
         <v>80</v>
       </c>
     </row>
@@ -13073,16 +13092,16 @@
       <c r="C489">
         <v>4471.6400000000003</v>
       </c>
-      <c r="D489" t="s">
+      <c r="D489" s="2" t="s">
         <v>670</v>
       </c>
-      <c r="E489" t="s">
+      <c r="E489" s="2" t="s">
         <v>668</v>
       </c>
-      <c r="F489">
+      <c r="F489" s="2">
         <v>78.787878787878697</v>
       </c>
-      <c r="G489">
+      <c r="G489" s="2">
         <v>75</v>
       </c>
     </row>
@@ -13349,16 +13368,16 @@
       <c r="C501">
         <v>158.58000000000001</v>
       </c>
-      <c r="D501" t="s">
+      <c r="D501" s="2" t="s">
         <v>672</v>
       </c>
-      <c r="E501" t="s">
+      <c r="E501" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="F501">
-        <v>100</v>
-      </c>
-      <c r="G501">
+      <c r="F501" s="2">
+        <v>100</v>
+      </c>
+      <c r="G501" s="2">
         <v>100</v>
       </c>
     </row>
@@ -13464,16 +13483,16 @@
       <c r="C506">
         <v>62.06</v>
       </c>
-      <c r="D506" t="s">
+      <c r="D506" s="2" t="s">
         <v>673</v>
       </c>
-      <c r="E506" t="s">
+      <c r="E506" s="2" t="s">
         <v>662</v>
       </c>
-      <c r="F506">
-        <v>100</v>
-      </c>
-      <c r="G506">
+      <c r="F506" s="2">
+        <v>100</v>
+      </c>
+      <c r="G506" s="2">
         <v>100</v>
       </c>
     </row>
@@ -13487,16 +13506,16 @@
       <c r="C507">
         <v>482.89</v>
       </c>
-      <c r="D507" t="s">
+      <c r="D507" s="2" t="s">
         <v>675</v>
       </c>
-      <c r="E507" t="s">
+      <c r="E507" s="2" t="s">
         <v>676</v>
       </c>
-      <c r="F507">
+      <c r="F507" s="2">
         <v>64.285714285714207</v>
       </c>
-      <c r="G507">
+      <c r="G507" s="2">
         <v>59.259259259259203</v>
       </c>
     </row>
@@ -13533,16 +13552,16 @@
       <c r="C509">
         <v>59.19</v>
       </c>
-      <c r="D509" t="s">
+      <c r="D509" s="2" t="s">
         <v>677</v>
       </c>
-      <c r="E509" t="s">
+      <c r="E509" s="2" t="s">
         <v>430</v>
       </c>
-      <c r="F509">
-        <v>100</v>
-      </c>
-      <c r="G509">
+      <c r="F509" s="2">
+        <v>100</v>
+      </c>
+      <c r="G509" s="2">
         <v>100</v>
       </c>
     </row>
@@ -13579,16 +13598,16 @@
       <c r="C511">
         <v>200.22</v>
       </c>
-      <c r="D511" t="s">
+      <c r="D511" s="2" t="s">
         <v>678</v>
       </c>
-      <c r="E511" t="s">
+      <c r="E511" s="2" t="s">
         <v>679</v>
       </c>
-      <c r="F511">
-        <v>100</v>
-      </c>
-      <c r="G511">
+      <c r="F511" s="2">
+        <v>100</v>
+      </c>
+      <c r="G511" s="2">
         <v>100</v>
       </c>
     </row>
@@ -13602,16 +13621,16 @@
       <c r="C512">
         <v>700.24</v>
       </c>
-      <c r="D512" t="s">
+      <c r="D512" s="2" t="s">
         <v>680</v>
       </c>
-      <c r="E512" t="s">
+      <c r="E512" s="2" t="s">
         <v>681</v>
       </c>
-      <c r="F512">
+      <c r="F512" s="2">
         <v>91.6666666666666</v>
       </c>
-      <c r="G512">
+      <c r="G512" s="2">
         <v>64.705882352941103</v>
       </c>
     </row>
@@ -13623,7 +13642,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="514" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="514" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A514" t="s">
         <v>684</v>
       </c>
@@ -13686,7 +13705,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="520" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="520" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A520" t="s">
         <v>5</v>
       </c>
@@ -13709,7 +13728,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="521" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="521" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A521" t="s">
         <v>5</v>
       </c>
@@ -13878,7 +13897,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="529" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="529" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A529" t="s">
         <v>708</v>
       </c>
@@ -14368,11 +14387,9 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:G589" xr:uid="{556460DC-71F1-43FF-BD31-36D25365B781}">
-    <filterColumn colId="3">
+    <filterColumn colId="1">
       <filters>
-        <filter val="Eagle (Dublin Gulch)"/>
-        <filter val="Eagle River"/>
-        <filter val="Eagle's Nest"/>
+        <filter val="2815"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/data/Mappings/mapping_npri.xlsx
+++ b/data/Mappings/mapping_npri.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://polymtlca-my.sharepoint.com/personal/marin_pellan_polymtl_ca/Documents/POST_DOC/CODE/metallican_db/data/Mappings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="69" documentId="13_ncr:1_{79931472-8B2F-4982-8306-AF8D7544F4B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{79F3E67D-279D-4663-B2A3-B2BF2D31F971}"/>
+  <xr:revisionPtr revIDLastSave="75" documentId="13_ncr:1_{79931472-8B2F-4982-8306-AF8D7544F4B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B2D7F925-9911-41D5-9D40-8FC9727F9A65}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-705" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-705" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="mapping" sheetId="1" r:id="rId1"/>
@@ -2398,11 +2398,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2687,11 +2686,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:B108"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
@@ -2702,7 +2702,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>444</v>
       </c>
@@ -2710,7 +2710,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>1070</v>
       </c>
@@ -2718,7 +2718,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>1071</v>
       </c>
@@ -2726,7 +2726,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>1106</v>
       </c>
@@ -2734,7 +2734,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>1148</v>
       </c>
@@ -2742,7 +2742,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>1149</v>
       </c>
@@ -2750,7 +2750,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>1233</v>
       </c>
@@ -2758,7 +2758,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>1236</v>
       </c>
@@ -2766,7 +2766,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>1303</v>
       </c>
@@ -2774,7 +2774,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>1465</v>
       </c>
@@ -2782,7 +2782,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>1467</v>
       </c>
@@ -2790,7 +2790,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>1471</v>
       </c>
@@ -2798,7 +2798,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>1520</v>
       </c>
@@ -2806,7 +2806,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>1568</v>
       </c>
@@ -2814,7 +2814,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>1651</v>
       </c>
@@ -2822,7 +2822,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>1941</v>
       </c>
@@ -2830,7 +2830,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>2000</v>
       </c>
@@ -2838,7 +2838,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>2038</v>
       </c>
@@ -2846,7 +2846,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>2100</v>
       </c>
@@ -2854,7 +2854,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>2132</v>
       </c>
@@ -2862,7 +2862,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>2372</v>
       </c>
@@ -2870,7 +2870,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>2710</v>
       </c>
@@ -2878,7 +2878,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>2740</v>
       </c>
@@ -2886,7 +2886,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>2978</v>
       </c>
@@ -2894,7 +2894,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>2984</v>
       </c>
@@ -2902,7 +2902,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>2986</v>
       </c>
@@ -2910,7 +2910,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>3060</v>
       </c>
@@ -2918,7 +2918,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>3062</v>
       </c>
@@ -2926,7 +2926,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>3158</v>
       </c>
@@ -2934,7 +2934,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>3197</v>
       </c>
@@ -2942,7 +2942,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>3356</v>
       </c>
@@ -2950,7 +2950,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>3406</v>
       </c>
@@ -2958,7 +2958,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>3411</v>
       </c>
@@ -2966,7 +2966,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>3598</v>
       </c>
@@ -2974,7 +2974,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>3623</v>
       </c>
@@ -2982,7 +2982,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>3649</v>
       </c>
@@ -2990,7 +2990,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>3713</v>
       </c>
@@ -2998,7 +2998,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>3802</v>
       </c>
@@ -3014,7 +3014,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>3824</v>
       </c>
@@ -3022,7 +3022,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>3916</v>
       </c>
@@ -3030,7 +3030,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>3991</v>
       </c>
@@ -3038,7 +3038,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>4045</v>
       </c>
@@ -3046,7 +3046,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>4169</v>
       </c>
@@ -3054,7 +3054,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>4197</v>
       </c>
@@ -3062,7 +3062,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>4778</v>
       </c>
@@ -3070,7 +3070,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>4782</v>
       </c>
@@ -3078,7 +3078,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>4806</v>
       </c>
@@ -3086,7 +3086,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>4866</v>
       </c>
@@ -3094,7 +3094,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>4868</v>
       </c>
@@ -3102,7 +3102,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>5013</v>
       </c>
@@ -3110,7 +3110,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>5102</v>
       </c>
@@ -3118,7 +3118,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>5219</v>
       </c>
@@ -3126,7 +3126,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>5448</v>
       </c>
@@ -3134,7 +3134,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>5460</v>
       </c>
@@ -3142,7 +3142,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>5510</v>
       </c>
@@ -3150,7 +3150,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>5656</v>
       </c>
@@ -3158,7 +3158,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>6093</v>
       </c>
@@ -3166,7 +3166,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>6217</v>
       </c>
@@ -3174,7 +3174,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>6344</v>
       </c>
@@ -3182,7 +3182,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>8015</v>
       </c>
@@ -3190,7 +3190,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>8757</v>
       </c>
@@ -3198,7 +3198,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>8778</v>
       </c>
@@ -3206,7 +3206,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>8783</v>
       </c>
@@ -3214,7 +3214,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>8803</v>
       </c>
@@ -3222,7 +3222,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>8807</v>
       </c>
@@ -3230,7 +3230,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>10010</v>
       </c>
@@ -3238,7 +3238,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>10153</v>
       </c>
@@ -3246,7 +3246,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>10199</v>
       </c>
@@ -3254,7 +3254,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>10201</v>
       </c>
@@ -3262,7 +3262,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>10202</v>
       </c>
@@ -3270,7 +3270,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A73" s="1">
         <v>10203</v>
       </c>
@@ -3278,7 +3278,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A74" s="1">
         <v>10204</v>
       </c>
@@ -3286,7 +3286,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>11123</v>
       </c>
@@ -3294,7 +3294,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>11154</v>
       </c>
@@ -3302,7 +3302,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>11454</v>
       </c>
@@ -3310,7 +3310,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>11588</v>
       </c>
@@ -3318,7 +3318,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>11794</v>
       </c>
@@ -3326,7 +3326,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>11796</v>
       </c>
@@ -3334,7 +3334,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>11867</v>
       </c>
@@ -3342,7 +3342,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>11878</v>
       </c>
@@ -3350,7 +3350,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>19397</v>
       </c>
@@ -3358,7 +3358,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>20131</v>
       </c>
@@ -3366,7 +3366,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>23273</v>
       </c>
@@ -3374,7 +3374,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>24216</v>
       </c>
@@ -3382,7 +3382,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>25188</v>
       </c>
@@ -3390,7 +3390,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A88">
         <v>25434</v>
       </c>
@@ -3398,7 +3398,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A89">
         <v>26132</v>
       </c>
@@ -3406,7 +3406,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>26423</v>
       </c>
@@ -3414,7 +3414,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A91">
         <v>27063</v>
       </c>
@@ -3422,7 +3422,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A92">
         <v>27853</v>
       </c>
@@ -3430,7 +3430,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A93">
         <v>28726</v>
       </c>
@@ -3438,7 +3438,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A94">
         <v>28761</v>
       </c>
@@ -3446,7 +3446,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A95">
         <v>29072</v>
       </c>
@@ -3454,7 +3454,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A96">
         <v>29191</v>
       </c>
@@ -3462,7 +3462,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A97">
         <v>29548</v>
       </c>
@@ -3470,7 +3470,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A98">
         <v>29877</v>
       </c>
@@ -3478,7 +3478,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A99">
         <v>30798</v>
       </c>
@@ -3486,7 +3486,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A100">
         <v>32235</v>
       </c>
@@ -3494,7 +3494,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A101">
         <v>32933</v>
       </c>
@@ -3502,7 +3502,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A102">
         <v>33049</v>
       </c>
@@ -3510,7 +3510,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A103">
         <v>33819</v>
       </c>
@@ -3518,7 +3518,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A104">
         <v>34014</v>
       </c>
@@ -3526,7 +3526,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A105" s="1">
         <v>99</v>
       </c>
@@ -3534,7 +3534,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A106" s="1">
         <v>29389</v>
       </c>
@@ -3542,7 +3542,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A107" s="1">
         <v>8600</v>
       </c>
@@ -3550,7 +3550,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A108" s="1">
         <v>32238</v>
       </c>
@@ -3560,6 +3560,11 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:B108" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="ON-MAIN-4e0734b5"/>
+      </filters>
+    </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B104">
       <sortCondition ref="A1:A104"/>
     </sortState>
@@ -3575,8 +3580,8 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.90625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="35.81640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="63.6328125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="22.453125" bestFit="1" customWidth="1"/>
@@ -7419,16 +7424,16 @@
       <c r="C198">
         <v>5713.75</v>
       </c>
-      <c r="D198" s="3" t="s">
+      <c r="D198" t="s">
         <v>370</v>
       </c>
-      <c r="E198" s="3" t="s">
+      <c r="E198" t="s">
         <v>357</v>
       </c>
-      <c r="F198" s="3">
+      <c r="F198">
         <v>72</v>
       </c>
-      <c r="G198" s="3">
+      <c r="G198">
         <v>70</v>
       </c>
     </row>
@@ -9711,7 +9716,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="317" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
         <v>500</v>
       </c>
@@ -9780,7 +9785,7 @@
         <v>32.258064516128997</v>
       </c>
     </row>
-    <row r="320" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
         <v>505</v>
       </c>
@@ -9872,7 +9877,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="324" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
         <v>49</v>
       </c>
@@ -10160,7 +10165,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="345" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
         <v>97</v>
       </c>
@@ -10229,7 +10234,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="348" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
         <v>60</v>
       </c>
@@ -14387,9 +14392,9 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:G589" xr:uid="{556460DC-71F1-43FF-BD31-36D25365B781}">
-    <filterColumn colId="1">
+    <filterColumn colId="3">
       <filters>
-        <filter val="2815"/>
+        <filter val="Timmins West"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/data/Mappings/mapping_npri.xlsx
+++ b/data/Mappings/mapping_npri.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://polymtlca-my.sharepoint.com/personal/marin_pellan_polymtl_ca/Documents/POST_DOC/CODE/metallican_db/data/Mappings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="75" documentId="13_ncr:1_{79931472-8B2F-4982-8306-AF8D7544F4B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B2D7F925-9911-41D5-9D40-8FC9727F9A65}"/>
+  <xr:revisionPtr revIDLastSave="88" documentId="13_ncr:1_{79931472-8B2F-4982-8306-AF8D7544F4B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C0973AF9-32CA-49D9-BBC8-F632070BEA8E}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-705" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-705" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="mapping" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">LT!$A$1:$G$589</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">mapping!$A$1:$B$108</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">mapping!$A$1:$B$109</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1635" uniqueCount="770">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1636" uniqueCount="770">
   <si>
     <t>npri_id</t>
   </si>
@@ -2417,10 +2417,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2686,8 +2682,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:B108"/>
+  <dimension ref="A1:C109"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.26953125" bestFit="1" customWidth="1"/>
@@ -2702,7 +2697,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>444</v>
       </c>
@@ -2710,7 +2705,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>1070</v>
       </c>
@@ -2718,7 +2713,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>1071</v>
       </c>
@@ -2726,7 +2721,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>1106</v>
       </c>
@@ -2734,7 +2729,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="6" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>1148</v>
       </c>
@@ -2742,7 +2737,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="7" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>1149</v>
       </c>
@@ -2750,7 +2745,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="8" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>1233</v>
       </c>
@@ -2758,7 +2753,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>1236</v>
       </c>
@@ -2766,7 +2761,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="10" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>1303</v>
       </c>
@@ -2774,7 +2769,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="11" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>1465</v>
       </c>
@@ -2782,7 +2777,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>1467</v>
       </c>
@@ -2790,7 +2785,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="13" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>1471</v>
       </c>
@@ -2798,7 +2793,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>1520</v>
       </c>
@@ -2806,7 +2801,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>1568</v>
       </c>
@@ -2814,7 +2809,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="16" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>1651</v>
       </c>
@@ -2822,7 +2817,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="17" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>1941</v>
       </c>
@@ -2830,7 +2825,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="18" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>2000</v>
       </c>
@@ -2838,7 +2833,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="19" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>2038</v>
       </c>
@@ -2846,7 +2841,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="20" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>2100</v>
       </c>
@@ -2854,7 +2849,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="21" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>2132</v>
       </c>
@@ -2862,7 +2857,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>2372</v>
       </c>
@@ -2870,7 +2865,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="23" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>2710</v>
       </c>
@@ -2878,7 +2873,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="24" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>2740</v>
       </c>
@@ -2886,7 +2881,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="25" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>2978</v>
       </c>
@@ -2894,7 +2889,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="26" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>2984</v>
       </c>
@@ -2902,7 +2897,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="27" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>2986</v>
       </c>
@@ -2910,7 +2905,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="28" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>3060</v>
       </c>
@@ -2918,7 +2913,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="29" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>3062</v>
       </c>
@@ -2926,7 +2921,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="30" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>3158</v>
       </c>
@@ -2934,7 +2929,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="31" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>3197</v>
       </c>
@@ -2942,7 +2937,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="32" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>3356</v>
       </c>
@@ -2950,7 +2945,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="33" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>3406</v>
       </c>
@@ -2958,7 +2953,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="34" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>3411</v>
       </c>
@@ -2966,7 +2961,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="35" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>3598</v>
       </c>
@@ -2974,7 +2969,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="36" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>3623</v>
       </c>
@@ -2982,7 +2977,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="37" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>3649</v>
       </c>
@@ -2990,7 +2985,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="38" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>3713</v>
       </c>
@@ -2998,7 +2993,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="39" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>3802</v>
       </c>
@@ -3014,7 +3009,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="41" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>3824</v>
       </c>
@@ -3022,7 +3017,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="42" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>3916</v>
       </c>
@@ -3030,7 +3025,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="43" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>3991</v>
       </c>
@@ -3038,7 +3033,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>4045</v>
       </c>
@@ -3046,7 +3041,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="45" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>4169</v>
       </c>
@@ -3054,7 +3049,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="46" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>4197</v>
       </c>
@@ -3062,7 +3057,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="47" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>4778</v>
       </c>
@@ -3070,7 +3065,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="48" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>4782</v>
       </c>
@@ -3078,7 +3073,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="49" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>4806</v>
       </c>
@@ -3086,7 +3081,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="50" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>4866</v>
       </c>
@@ -3094,7 +3089,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="51" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>4868</v>
       </c>
@@ -3102,7 +3097,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="52" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>5013</v>
       </c>
@@ -3110,7 +3105,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="53" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>5102</v>
       </c>
@@ -3118,7 +3113,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="54" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>5219</v>
       </c>
@@ -3126,7 +3121,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="55" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>5448</v>
       </c>
@@ -3134,7 +3129,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="56" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>5460</v>
       </c>
@@ -3142,7 +3137,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="57" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>5510</v>
       </c>
@@ -3150,7 +3145,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="58" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>5656</v>
       </c>
@@ -3158,7 +3153,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="59" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>6093</v>
       </c>
@@ -3166,7 +3161,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="60" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>6217</v>
       </c>
@@ -3174,7 +3169,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="61" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>6344</v>
       </c>
@@ -3182,7 +3177,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="62" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>8015</v>
       </c>
@@ -3190,7 +3185,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="63" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>8757</v>
       </c>
@@ -3198,7 +3193,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="64" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>8778</v>
       </c>
@@ -3206,7 +3201,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="65" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>8783</v>
       </c>
@@ -3214,7 +3209,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="66" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>8803</v>
       </c>
@@ -3222,7 +3217,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="67" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>8807</v>
       </c>
@@ -3230,7 +3225,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="68" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>10010</v>
       </c>
@@ -3238,7 +3233,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="69" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>10153</v>
       </c>
@@ -3246,7 +3241,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="70" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>10199</v>
       </c>
@@ -3254,7 +3249,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="71" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>10201</v>
       </c>
@@ -3262,7 +3257,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="72" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>10202</v>
       </c>
@@ -3270,7 +3265,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="73" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A73" s="1">
         <v>10203</v>
       </c>
@@ -3278,7 +3273,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="74" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A74" s="1">
         <v>10204</v>
       </c>
@@ -3286,7 +3281,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="75" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>11123</v>
       </c>
@@ -3294,7 +3289,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="76" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>11154</v>
       </c>
@@ -3302,7 +3297,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="77" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>11454</v>
       </c>
@@ -3310,7 +3305,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="78" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>11588</v>
       </c>
@@ -3318,7 +3313,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="79" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>11794</v>
       </c>
@@ -3326,7 +3321,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="80" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>11796</v>
       </c>
@@ -3334,7 +3329,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="81" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>11867</v>
       </c>
@@ -3342,7 +3337,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="82" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>11878</v>
       </c>
@@ -3350,7 +3345,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="83" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>19397</v>
       </c>
@@ -3358,7 +3353,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="84" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>20131</v>
       </c>
@@ -3366,7 +3361,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="85" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>23273</v>
       </c>
@@ -3374,7 +3369,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="86" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>24216</v>
       </c>
@@ -3382,7 +3377,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="87" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>25188</v>
       </c>
@@ -3390,7 +3385,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="88" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A88">
         <v>25434</v>
       </c>
@@ -3398,7 +3393,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="89" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A89">
         <v>26132</v>
       </c>
@@ -3406,7 +3401,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="90" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>26423</v>
       </c>
@@ -3414,7 +3409,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="91" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A91">
         <v>27063</v>
       </c>
@@ -3422,7 +3417,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="92" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A92">
         <v>27853</v>
       </c>
@@ -3430,7 +3425,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="93" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A93">
         <v>28726</v>
       </c>
@@ -3438,7 +3433,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="94" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A94">
         <v>28761</v>
       </c>
@@ -3446,7 +3441,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="95" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A95">
         <v>29072</v>
       </c>
@@ -3454,7 +3449,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="96" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A96">
         <v>29191</v>
       </c>
@@ -3462,7 +3457,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="97" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A97">
         <v>29548</v>
       </c>
@@ -3470,7 +3465,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="98" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A98">
         <v>29877</v>
       </c>
@@ -3478,7 +3473,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="99" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A99">
         <v>30798</v>
       </c>
@@ -3486,7 +3481,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="100" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A100">
         <v>32235</v>
       </c>
@@ -3494,7 +3489,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="101" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A101">
         <v>32933</v>
       </c>
@@ -3502,7 +3497,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="102" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A102">
         <v>33049</v>
       </c>
@@ -3510,7 +3505,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="103" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A103">
         <v>33819</v>
       </c>
@@ -3518,7 +3513,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="104" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A104">
         <v>34014</v>
       </c>
@@ -3526,7 +3521,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="105" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A105" s="1">
         <v>99</v>
       </c>
@@ -3534,7 +3529,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="106" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A106" s="1">
         <v>29389</v>
       </c>
@@ -3542,7 +3537,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="107" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A107" s="1">
         <v>8600</v>
       </c>
@@ -3550,7 +3545,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="108" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A108" s="1">
         <v>32238</v>
       </c>
@@ -3558,13 +3553,17 @@
         <v>684</v>
       </c>
     </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A109" s="2">
+        <v>21543</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="C109" s="2"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B108" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="ON-MAIN-4e0734b5"/>
-      </filters>
-    </filterColumn>
+  <autoFilter ref="A1:B109" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B104">
       <sortCondition ref="A1:A104"/>
     </sortState>
@@ -7900,7 +7899,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="225" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
         <v>403</v>
       </c>
@@ -7923,7 +7922,7 @@
         <v>57.142857142857103</v>
       </c>
     </row>
-    <row r="226" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
         <v>403</v>
       </c>
@@ -7946,30 +7945,30 @@
         <v>21.428571428571399</v>
       </c>
     </row>
-    <row r="227" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A227" t="s">
+    <row r="227" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A227" s="2" t="s">
         <v>403</v>
       </c>
-      <c r="B227">
+      <c r="B227" s="2">
         <v>21543</v>
       </c>
-      <c r="C227">
+      <c r="C227" s="2">
         <v>4093.57</v>
       </c>
-      <c r="D227" t="s">
+      <c r="D227" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="E227" t="s">
+      <c r="E227" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="F227">
+      <c r="F227" s="2">
         <v>60</v>
       </c>
-      <c r="G227">
+      <c r="G227" s="2">
         <v>57.142857142857103</v>
       </c>
     </row>
-    <row r="228" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
         <v>14</v>
       </c>
@@ -7992,7 +7991,7 @@
         <v>31.25</v>
       </c>
     </row>
-    <row r="229" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
         <v>14</v>
       </c>
@@ -8015,7 +8014,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="230" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
         <v>14</v>
       </c>
@@ -8046,7 +8045,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="232" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
         <v>25</v>
       </c>
@@ -8069,7 +8068,7 @@
         <v>57.142857142857103</v>
       </c>
     </row>
-    <row r="233" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
         <v>25</v>
       </c>
@@ -8092,7 +8091,7 @@
         <v>21.428571428571399</v>
       </c>
     </row>
-    <row r="234" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
         <v>25</v>
       </c>
@@ -10234,7 +10233,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="348" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
         <v>60</v>
       </c>
@@ -14392,9 +14391,11 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:G589" xr:uid="{556460DC-71F1-43FF-BD31-36D25365B781}">
-    <filterColumn colId="3">
+    <filterColumn colId="0">
       <filters>
-        <filter val="Timmins West"/>
+        <filter val="MB-MAIN-0898e255"/>
+        <filter val="MB-MAIN-be5b3dc8"/>
+        <filter val="MB-MAIN-da0b5c3d"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/data/Mappings/mapping_npri.xlsx
+++ b/data/Mappings/mapping_npri.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://polymtlca-my.sharepoint.com/personal/marin_pellan_polymtl_ca/Documents/POST_DOC/CODE/metallican_db/data/Mappings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="88" documentId="13_ncr:1_{79931472-8B2F-4982-8306-AF8D7544F4B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C0973AF9-32CA-49D9-BBC8-F632070BEA8E}"/>
+  <xr:revisionPtr revIDLastSave="106" documentId="13_ncr:1_{79931472-8B2F-4982-8306-AF8D7544F4B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7EA15784-F0F4-4065-A079-BE74AF868BD0}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-705" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="mapping" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">LT!$A$1:$G$589</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">mapping!$A$1:$B$109</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">mapping!$A$1:$B$110</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1636" uniqueCount="770">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1638" uniqueCount="770">
   <si>
     <t>npri_id</t>
   </si>
@@ -2417,6 +2417,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2682,14 +2686,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C109"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:C111"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.08984375" customWidth="1"/>
+    <col min="1" max="1" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2697,7 +2701,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>444</v>
       </c>
@@ -2705,7 +2709,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1070</v>
       </c>
@@ -2713,7 +2717,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1071</v>
       </c>
@@ -2721,7 +2725,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>1106</v>
       </c>
@@ -2729,7 +2733,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>1148</v>
       </c>
@@ -2737,7 +2741,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>1149</v>
       </c>
@@ -2745,7 +2749,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>1233</v>
       </c>
@@ -2753,7 +2757,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>1236</v>
       </c>
@@ -2761,7 +2765,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>1303</v>
       </c>
@@ -2769,7 +2773,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>1465</v>
       </c>
@@ -2777,7 +2781,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>1467</v>
       </c>
@@ -2785,7 +2789,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>1471</v>
       </c>
@@ -2793,7 +2797,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>1520</v>
       </c>
@@ -2801,7 +2805,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>1568</v>
       </c>
@@ -2809,7 +2813,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>1651</v>
       </c>
@@ -2817,7 +2821,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>1941</v>
       </c>
@@ -2825,7 +2829,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>2000</v>
       </c>
@@ -2833,7 +2837,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>2038</v>
       </c>
@@ -2841,7 +2845,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>2100</v>
       </c>
@@ -2849,7 +2853,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>2132</v>
       </c>
@@ -2857,7 +2861,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>2372</v>
       </c>
@@ -2865,7 +2869,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>2710</v>
       </c>
@@ -2873,7 +2877,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>2740</v>
       </c>
@@ -2881,7 +2885,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>2978</v>
       </c>
@@ -2889,7 +2893,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>2984</v>
       </c>
@@ -2897,7 +2901,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>2986</v>
       </c>
@@ -2905,7 +2909,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>3060</v>
       </c>
@@ -2913,7 +2917,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>3062</v>
       </c>
@@ -2921,7 +2925,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>3158</v>
       </c>
@@ -2929,7 +2933,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>3197</v>
       </c>
@@ -2937,7 +2941,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>3356</v>
       </c>
@@ -2945,7 +2949,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>3406</v>
       </c>
@@ -2953,7 +2957,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>3411</v>
       </c>
@@ -2961,7 +2965,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>3598</v>
       </c>
@@ -2969,7 +2973,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>3623</v>
       </c>
@@ -2977,7 +2981,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>3649</v>
       </c>
@@ -2985,7 +2989,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>3713</v>
       </c>
@@ -2993,7 +2997,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>3802</v>
       </c>
@@ -3001,7 +3005,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>3810</v>
       </c>
@@ -3009,7 +3013,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>3824</v>
       </c>
@@ -3017,7 +3021,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>3916</v>
       </c>
@@ -3025,7 +3029,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>3991</v>
       </c>
@@ -3033,7 +3037,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>4045</v>
       </c>
@@ -3041,7 +3045,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>4169</v>
       </c>
@@ -3049,7 +3053,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>4197</v>
       </c>
@@ -3057,7 +3061,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>4778</v>
       </c>
@@ -3065,7 +3069,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>4782</v>
       </c>
@@ -3073,7 +3077,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>4806</v>
       </c>
@@ -3081,7 +3085,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>4866</v>
       </c>
@@ -3089,7 +3093,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>4868</v>
       </c>
@@ -3097,7 +3101,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>5013</v>
       </c>
@@ -3105,7 +3109,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>5102</v>
       </c>
@@ -3113,7 +3117,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>5219</v>
       </c>
@@ -3121,7 +3125,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>5448</v>
       </c>
@@ -3129,7 +3133,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>5460</v>
       </c>
@@ -3137,7 +3141,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>5510</v>
       </c>
@@ -3145,7 +3149,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>5656</v>
       </c>
@@ -3153,7 +3157,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>6093</v>
       </c>
@@ -3161,7 +3165,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>6217</v>
       </c>
@@ -3169,7 +3173,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>6344</v>
       </c>
@@ -3177,7 +3181,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>8015</v>
       </c>
@@ -3185,7 +3189,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>8757</v>
       </c>
@@ -3193,7 +3197,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>8778</v>
       </c>
@@ -3201,7 +3205,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>8783</v>
       </c>
@@ -3209,7 +3213,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>8803</v>
       </c>
@@ -3217,7 +3221,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>8807</v>
       </c>
@@ -3225,7 +3229,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>10010</v>
       </c>
@@ -3233,7 +3237,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>10153</v>
       </c>
@@ -3241,7 +3245,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>10199</v>
       </c>
@@ -3249,7 +3253,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>10201</v>
       </c>
@@ -3257,7 +3261,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>10202</v>
       </c>
@@ -3265,7 +3269,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>10203</v>
       </c>
@@ -3273,7 +3277,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>10204</v>
       </c>
@@ -3281,7 +3285,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>11123</v>
       </c>
@@ -3289,7 +3293,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>11154</v>
       </c>
@@ -3297,7 +3301,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>11454</v>
       </c>
@@ -3305,7 +3309,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>11588</v>
       </c>
@@ -3313,7 +3317,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>11794</v>
       </c>
@@ -3321,7 +3325,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>11796</v>
       </c>
@@ -3329,7 +3333,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>11867</v>
       </c>
@@ -3337,7 +3341,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>11878</v>
       </c>
@@ -3345,7 +3349,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>19397</v>
       </c>
@@ -3353,7 +3357,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>20131</v>
       </c>
@@ -3361,7 +3365,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>23273</v>
       </c>
@@ -3369,7 +3373,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>24216</v>
       </c>
@@ -3377,7 +3381,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>25188</v>
       </c>
@@ -3385,7 +3389,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>25434</v>
       </c>
@@ -3393,7 +3397,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>26132</v>
       </c>
@@ -3401,7 +3405,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>26423</v>
       </c>
@@ -3409,7 +3413,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>27063</v>
       </c>
@@ -3417,7 +3421,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>27853</v>
       </c>
@@ -3425,7 +3429,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>28726</v>
       </c>
@@ -3433,7 +3437,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>28761</v>
       </c>
@@ -3441,7 +3445,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>29072</v>
       </c>
@@ -3449,7 +3453,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>29191</v>
       </c>
@@ -3457,7 +3461,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>29548</v>
       </c>
@@ -3465,7 +3469,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>29877</v>
       </c>
@@ -3473,7 +3477,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>30798</v>
       </c>
@@ -3481,7 +3485,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>32235</v>
       </c>
@@ -3489,7 +3493,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>32933</v>
       </c>
@@ -3497,7 +3501,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>33049</v>
       </c>
@@ -3505,7 +3509,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>33819</v>
       </c>
@@ -3513,7 +3517,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>34014</v>
       </c>
@@ -3521,7 +3525,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
         <v>99</v>
       </c>
@@ -3529,7 +3533,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
         <v>29389</v>
       </c>
@@ -3537,7 +3541,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
         <v>8600</v>
       </c>
@@ -3545,7 +3549,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
         <v>32238</v>
       </c>
@@ -3553,7 +3557,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" s="2">
         <v>21543</v>
       </c>
@@ -3562,8 +3566,24 @@
       </c>
       <c r="C109" s="2"/>
     </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110">
+        <v>27059</v>
+      </c>
+      <c r="B110" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111">
+        <v>1473</v>
+      </c>
+      <c r="B111" t="s">
+        <v>674</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B109" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <autoFilter ref="A1:B110" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B104">
       <sortCondition ref="A1:A104"/>
     </sortState>
@@ -3576,18 +3596,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{556460DC-71F1-43FF-BD31-36D25365B781}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:G589"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.90625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="35.81640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="63.6328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.453125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="63.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -3610,7 +3630,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="2" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>103</v>
       </c>
@@ -3633,7 +3653,7 @@
         <v>27.7777777777777</v>
       </c>
     </row>
-    <row r="3" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>106</v>
       </c>
@@ -3641,7 +3661,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="4" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>108</v>
       </c>
@@ -3664,7 +3684,7 @@
         <v>15.3846153846153</v>
       </c>
     </row>
-    <row r="5" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>111</v>
       </c>
@@ -3672,7 +3692,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="6" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>45</v>
       </c>
@@ -3695,7 +3715,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>45</v>
       </c>
@@ -3718,7 +3738,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>45</v>
       </c>
@@ -3741,7 +3761,7 @@
         <v>31.578947368421002</v>
       </c>
     </row>
-    <row r="9" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>68</v>
       </c>
@@ -3764,7 +3784,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="10" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>32</v>
       </c>
@@ -3787,7 +3807,7 @@
         <v>14.285714285714199</v>
       </c>
     </row>
-    <row r="11" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>32</v>
       </c>
@@ -3810,7 +3830,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="12" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>32</v>
       </c>
@@ -3833,7 +3853,7 @@
         <v>29.629629629629601</v>
       </c>
     </row>
-    <row r="13" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>120</v>
       </c>
@@ -3856,7 +3876,7 @@
         <v>52.173913043478201</v>
       </c>
     </row>
-    <row r="14" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>120</v>
       </c>
@@ -3879,7 +3899,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="15" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>81</v>
       </c>
@@ -3902,7 +3922,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="16" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>70</v>
       </c>
@@ -3925,7 +3945,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="17" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>128</v>
       </c>
@@ -3933,7 +3953,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>130</v>
       </c>
@@ -3941,7 +3961,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="19" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>132</v>
       </c>
@@ -3949,7 +3969,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="20" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>85</v>
       </c>
@@ -3972,7 +3992,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>85</v>
       </c>
@@ -3995,7 +4015,7 @@
         <v>23.529411764705799</v>
       </c>
     </row>
-    <row r="22" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>37</v>
       </c>
@@ -4018,7 +4038,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>47</v>
       </c>
@@ -4041,7 +4061,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>29</v>
       </c>
@@ -4064,7 +4084,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>29</v>
       </c>
@@ -4087,7 +4107,7 @@
         <v>11.1111111111111</v>
       </c>
     </row>
-    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>143</v>
       </c>
@@ -4110,7 +4130,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>143</v>
       </c>
@@ -4133,7 +4153,7 @@
         <v>10.5263157894736</v>
       </c>
     </row>
-    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>143</v>
       </c>
@@ -4156,7 +4176,7 @@
         <v>14.285714285714199</v>
       </c>
     </row>
-    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>143</v>
       </c>
@@ -4179,7 +4199,7 @@
         <v>18.181818181818102</v>
       </c>
     </row>
-    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>143</v>
       </c>
@@ -4202,7 +4222,7 @@
         <v>22.2222222222222</v>
       </c>
     </row>
-    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>143</v>
       </c>
@@ -4225,7 +4245,7 @@
         <v>7.8431372549019596</v>
       </c>
     </row>
-    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>143</v>
       </c>
@@ -4248,7 +4268,7 @@
         <v>19.047619047619001</v>
       </c>
     </row>
-    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>143</v>
       </c>
@@ -4271,7 +4291,7 @@
         <v>23.529411764705799</v>
       </c>
     </row>
-    <row r="34" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>143</v>
       </c>
@@ -4294,7 +4314,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="35" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>44</v>
       </c>
@@ -4317,7 +4337,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="36" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>44</v>
       </c>
@@ -4340,7 +4360,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="37" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>44</v>
       </c>
@@ -4363,7 +4383,7 @@
         <v>23.076923076922998</v>
       </c>
     </row>
-    <row r="38" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>40</v>
       </c>
@@ -4386,7 +4406,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="39" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>40</v>
       </c>
@@ -4409,7 +4429,7 @@
         <v>66.6666666666666</v>
       </c>
     </row>
-    <row r="40" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>161</v>
       </c>
@@ -4417,7 +4437,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="41" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>163</v>
       </c>
@@ -4425,7 +4445,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="42" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>91</v>
       </c>
@@ -4448,7 +4468,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="43" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>91</v>
       </c>
@@ -4471,7 +4491,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="44" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>53</v>
       </c>
@@ -4494,7 +4514,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="45" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>72</v>
       </c>
@@ -4517,7 +4537,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="46" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>72</v>
       </c>
@@ -4540,7 +4560,7 @@
         <v>14.285714285714199</v>
       </c>
     </row>
-    <row r="47" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>71</v>
       </c>
@@ -4563,7 +4583,7 @@
         <v>52.173913043478201</v>
       </c>
     </row>
-    <row r="48" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>71</v>
       </c>
@@ -4586,7 +4606,7 @@
         <v>59.090909090909001</v>
       </c>
     </row>
-    <row r="49" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>71</v>
       </c>
@@ -4609,7 +4629,7 @@
         <v>13.043478260869501</v>
       </c>
     </row>
-    <row r="50" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>71</v>
       </c>
@@ -4632,7 +4652,7 @@
         <v>27.906976744186</v>
       </c>
     </row>
-    <row r="51" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>71</v>
       </c>
@@ -4655,7 +4675,7 @@
         <v>38.709677419354797</v>
       </c>
     </row>
-    <row r="52" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>38</v>
       </c>
@@ -4678,7 +4698,7 @@
         <v>56.521739130434703</v>
       </c>
     </row>
-    <row r="53" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>38</v>
       </c>
@@ -4701,7 +4721,7 @@
         <v>54.545454545454497</v>
       </c>
     </row>
-    <row r="54" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>38</v>
       </c>
@@ -4724,7 +4744,7 @@
         <v>8.6956521739130395</v>
       </c>
     </row>
-    <row r="55" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>38</v>
       </c>
@@ -4747,7 +4767,7 @@
         <v>32.558139534883701</v>
       </c>
     </row>
-    <row r="56" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>38</v>
       </c>
@@ -4770,7 +4790,7 @@
         <v>38.709677419354797</v>
       </c>
     </row>
-    <row r="57" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>54</v>
       </c>
@@ -4793,7 +4813,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="58" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>74</v>
       </c>
@@ -4816,7 +4836,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="59" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>74</v>
       </c>
@@ -4839,7 +4859,7 @@
         <v>76.470588235294102</v>
       </c>
     </row>
-    <row r="60" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>74</v>
       </c>
@@ -4862,7 +4882,7 @@
         <v>30.769230769230699</v>
       </c>
     </row>
-    <row r="61" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>74</v>
       </c>
@@ -4885,7 +4905,7 @@
         <v>29.090909090909001</v>
       </c>
     </row>
-    <row r="62" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>74</v>
       </c>
@@ -4908,7 +4928,7 @@
         <v>29.090909090909001</v>
       </c>
     </row>
-    <row r="63" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>74</v>
       </c>
@@ -4931,7 +4951,7 @@
         <v>23.8095238095238</v>
       </c>
     </row>
-    <row r="64" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>74</v>
       </c>
@@ -4954,7 +4974,7 @@
         <v>37.5</v>
       </c>
     </row>
-    <row r="65" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>74</v>
       </c>
@@ -4977,7 +4997,7 @@
         <v>27.450980392156801</v>
       </c>
     </row>
-    <row r="66" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>74</v>
       </c>
@@ -5000,7 +5020,7 @@
         <v>20.689655172413701</v>
       </c>
     </row>
-    <row r="67" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>74</v>
       </c>
@@ -5023,7 +5043,7 @@
         <v>26.315789473684202</v>
       </c>
     </row>
-    <row r="68" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>74</v>
       </c>
@@ -5046,7 +5066,7 @@
         <v>30.769230769230699</v>
       </c>
     </row>
-    <row r="69" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>57</v>
       </c>
@@ -5069,7 +5089,7 @@
         <v>27.272727272727199</v>
       </c>
     </row>
-    <row r="70" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>57</v>
       </c>
@@ -5092,7 +5112,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="71" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>194</v>
       </c>
@@ -5100,7 +5120,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="72" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>2</v>
       </c>
@@ -5123,7 +5143,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="73" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>2</v>
       </c>
@@ -5146,7 +5166,7 @@
         <v>25.806451612903199</v>
       </c>
     </row>
-    <row r="74" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>2</v>
       </c>
@@ -5169,7 +5189,7 @@
         <v>24.2424242424242</v>
       </c>
     </row>
-    <row r="75" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>2</v>
       </c>
@@ -5192,7 +5212,7 @@
         <v>22.2222222222222</v>
       </c>
     </row>
-    <row r="76" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>2</v>
       </c>
@@ -5215,7 +5235,7 @@
         <v>22.2222222222222</v>
       </c>
     </row>
-    <row r="77" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>2</v>
       </c>
@@ -5238,7 +5258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>2</v>
       </c>
@@ -5261,7 +5281,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>2</v>
       </c>
@@ -5284,7 +5304,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="80" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>2</v>
       </c>
@@ -5307,7 +5327,7 @@
         <v>6.6666666666666696</v>
       </c>
     </row>
-    <row r="81" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>2</v>
       </c>
@@ -5330,7 +5350,7 @@
         <v>27.272727272727199</v>
       </c>
     </row>
-    <row r="82" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>207</v>
       </c>
@@ -5338,7 +5358,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="83" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>209</v>
       </c>
@@ -5346,7 +5366,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="84" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>211</v>
       </c>
@@ -5354,7 +5374,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="85" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>43</v>
       </c>
@@ -5377,7 +5397,7 @@
         <v>55.172413793103402</v>
       </c>
     </row>
-    <row r="86" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>215</v>
       </c>
@@ -5385,7 +5405,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="87" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>217</v>
       </c>
@@ -5393,7 +5413,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="88" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>219</v>
       </c>
@@ -5401,7 +5421,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="89" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>221</v>
       </c>
@@ -5409,7 +5429,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="90" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>223</v>
       </c>
@@ -5417,7 +5437,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="91" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>225</v>
       </c>
@@ -5425,30 +5445,30 @@
         <v>226</v>
       </c>
     </row>
-    <row r="92" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="B92">
-        <v>19397</v>
+        <v>1147</v>
       </c>
       <c r="C92">
-        <v>77.88</v>
+        <v>18014.560000000001</v>
       </c>
       <c r="D92" t="s">
-        <v>227</v>
+        <v>537</v>
       </c>
       <c r="E92" t="s">
-        <v>228</v>
+        <v>538</v>
       </c>
       <c r="F92">
-        <v>100</v>
+        <v>52.173913043478201</v>
       </c>
       <c r="G92">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>84</v>
       </c>
@@ -5471,7 +5491,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="94" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>39</v>
       </c>
@@ -5494,7 +5514,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="95" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>233</v>
       </c>
@@ -5517,7 +5537,7 @@
         <v>19.047619047619001</v>
       </c>
     </row>
-    <row r="96" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>236</v>
       </c>
@@ -5540,7 +5560,7 @@
         <v>9.0909090909090899</v>
       </c>
     </row>
-    <row r="97" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>236</v>
       </c>
@@ -5563,7 +5583,7 @@
         <v>38.461538461538403</v>
       </c>
     </row>
-    <row r="98" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>240</v>
       </c>
@@ -5571,7 +5591,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="99" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>242</v>
       </c>
@@ -5579,7 +5599,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="100" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>244</v>
       </c>
@@ -5587,7 +5607,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="101" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>246</v>
       </c>
@@ -5595,7 +5615,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="102" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>248</v>
       </c>
@@ -5603,7 +5623,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="103" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>250</v>
       </c>
@@ -5611,7 +5631,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="104" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>94</v>
       </c>
@@ -5634,7 +5654,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="105" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>79</v>
       </c>
@@ -5657,7 +5677,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="106" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>48</v>
       </c>
@@ -5680,7 +5700,7 @@
         <v>20.689655172413701</v>
       </c>
     </row>
-    <row r="107" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>48</v>
       </c>
@@ -5703,7 +5723,7 @@
         <v>66.6666666666666</v>
       </c>
     </row>
-    <row r="108" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>257</v>
       </c>
@@ -5711,7 +5731,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="109" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>259</v>
       </c>
@@ -5719,7 +5739,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="110" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>261</v>
       </c>
@@ -5727,7 +5747,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="111" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>263</v>
       </c>
@@ -5735,7 +5755,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="112" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>265</v>
       </c>
@@ -5743,7 +5763,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="113" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>267</v>
       </c>
@@ -5751,7 +5771,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="114" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>269</v>
       </c>
@@ -5774,7 +5794,7 @@
         <v>23.529411764705799</v>
       </c>
     </row>
-    <row r="115" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>269</v>
       </c>
@@ -5797,7 +5817,7 @@
         <v>33.3333333333333</v>
       </c>
     </row>
-    <row r="116" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>269</v>
       </c>
@@ -5820,7 +5840,7 @@
         <v>20.8333333333333</v>
       </c>
     </row>
-    <row r="117" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>269</v>
       </c>
@@ -5843,7 +5863,7 @@
         <v>22.727272727272702</v>
       </c>
     </row>
-    <row r="118" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>269</v>
       </c>
@@ -5866,7 +5886,7 @@
         <v>22.857142857142801</v>
       </c>
     </row>
-    <row r="119" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>275</v>
       </c>
@@ -5874,7 +5894,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="120" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>277</v>
       </c>
@@ -5882,7 +5902,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="121" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>279</v>
       </c>
@@ -5905,7 +5925,7 @@
         <v>18.75</v>
       </c>
     </row>
-    <row r="122" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>282</v>
       </c>
@@ -5913,7 +5933,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="123" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>284</v>
       </c>
@@ -5921,7 +5941,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="124" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>286</v>
       </c>
@@ -5929,7 +5949,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="125" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>288</v>
       </c>
@@ -5952,7 +5972,7 @@
         <v>9.0909090909090899</v>
       </c>
     </row>
-    <row r="126" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>288</v>
       </c>
@@ -5975,7 +5995,7 @@
         <v>11.764705882352899</v>
       </c>
     </row>
-    <row r="127" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>288</v>
       </c>
@@ -5998,7 +6018,7 @@
         <v>21.428571428571399</v>
       </c>
     </row>
-    <row r="128" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>8</v>
       </c>
@@ -6021,7 +6041,7 @@
         <v>20.5128205128205</v>
       </c>
     </row>
-    <row r="129" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>8</v>
       </c>
@@ -6044,7 +6064,7 @@
         <v>29.787234042553099</v>
       </c>
     </row>
-    <row r="130" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>6</v>
       </c>
@@ -6067,7 +6087,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="131" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>6</v>
       </c>
@@ -6090,7 +6110,7 @@
         <v>86.956521739130395</v>
       </c>
     </row>
-    <row r="132" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>6</v>
       </c>
@@ -6113,7 +6133,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="133" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>6</v>
       </c>
@@ -6136,7 +6156,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="134" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>6</v>
       </c>
@@ -6159,7 +6179,7 @@
         <v>18.181818181818102</v>
       </c>
     </row>
-    <row r="135" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>6</v>
       </c>
@@ -6182,7 +6202,7 @@
         <v>21.428571428571399</v>
       </c>
     </row>
-    <row r="136" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>6</v>
       </c>
@@ -6205,7 +6225,7 @@
         <v>19.672131147540899</v>
       </c>
     </row>
-    <row r="137" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>6</v>
       </c>
@@ -6228,7 +6248,7 @@
         <v>25.806451612903199</v>
       </c>
     </row>
-    <row r="138" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>6</v>
       </c>
@@ -6251,7 +6271,7 @@
         <v>22.2222222222222</v>
       </c>
     </row>
-    <row r="139" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>6</v>
       </c>
@@ -6274,7 +6294,7 @@
         <v>23.8095238095238</v>
       </c>
     </row>
-    <row r="140" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>93</v>
       </c>
@@ -6297,7 +6317,7 @@
         <v>60.606060606060602</v>
       </c>
     </row>
-    <row r="141" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>93</v>
       </c>
@@ -6320,7 +6340,7 @@
         <v>46.511627906976699</v>
       </c>
     </row>
-    <row r="142" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>93</v>
       </c>
@@ -6343,7 +6363,7 @@
         <v>31.25</v>
       </c>
     </row>
-    <row r="143" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>77</v>
       </c>
@@ -6366,7 +6386,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="144" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>77</v>
       </c>
@@ -6389,7 +6409,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="145" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>55</v>
       </c>
@@ -6412,7 +6432,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="146" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>15</v>
       </c>
@@ -6435,7 +6455,7 @@
         <v>62.857142857142797</v>
       </c>
     </row>
-    <row r="147" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>15</v>
       </c>
@@ -6458,7 +6478,7 @@
         <v>48.8888888888888</v>
       </c>
     </row>
-    <row r="148" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>15</v>
       </c>
@@ -6481,7 +6501,7 @@
         <v>58.823529411764703</v>
       </c>
     </row>
-    <row r="149" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>87</v>
       </c>
@@ -6504,7 +6524,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="150" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>50</v>
       </c>
@@ -6527,7 +6547,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="151" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>306</v>
       </c>
@@ -6535,7 +6555,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="152" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>308</v>
       </c>
@@ -6543,7 +6563,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="153" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>310</v>
       </c>
@@ -6551,7 +6571,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="154" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>312</v>
       </c>
@@ -6559,7 +6579,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="155" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>314</v>
       </c>
@@ -6567,7 +6587,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="156" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>316</v>
       </c>
@@ -6575,7 +6595,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="157" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>318</v>
       </c>
@@ -6583,7 +6603,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="158" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>320</v>
       </c>
@@ -6591,7 +6611,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="159" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>322</v>
       </c>
@@ -6599,7 +6619,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="160" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>324</v>
       </c>
@@ -6607,7 +6627,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="161" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>326</v>
       </c>
@@ -6615,7 +6635,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="162" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>328</v>
       </c>
@@ -6623,7 +6643,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="163" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>330</v>
       </c>
@@ -6631,7 +6651,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="164" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>332</v>
       </c>
@@ -6654,7 +6674,7 @@
         <v>27.118644067796598</v>
       </c>
     </row>
-    <row r="165" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>332</v>
       </c>
@@ -6677,7 +6697,7 @@
         <v>28.571428571428498</v>
       </c>
     </row>
-    <row r="166" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>332</v>
       </c>
@@ -6700,7 +6720,7 @@
         <v>16.326530612244799</v>
       </c>
     </row>
-    <row r="167" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>332</v>
       </c>
@@ -6723,7 +6743,7 @@
         <v>4.6511627906976596</v>
       </c>
     </row>
-    <row r="168" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>332</v>
       </c>
@@ -6746,7 +6766,7 @@
         <v>30.136986301369799</v>
       </c>
     </row>
-    <row r="169" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>336</v>
       </c>
@@ -6769,7 +6789,7 @@
         <v>26.6666666666666</v>
       </c>
     </row>
-    <row r="170" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>339</v>
       </c>
@@ -6792,7 +6812,7 @@
         <v>57.142857142857103</v>
       </c>
     </row>
-    <row r="171" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>339</v>
       </c>
@@ -6815,7 +6835,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="172" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>26</v>
       </c>
@@ -6838,7 +6858,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="173" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>26</v>
       </c>
@@ -6861,7 +6881,7 @@
         <v>11.4285714285714</v>
       </c>
     </row>
-    <row r="174" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>58</v>
       </c>
@@ -6884,7 +6904,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="175" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>41</v>
       </c>
@@ -6907,7 +6927,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="176" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>41</v>
       </c>
@@ -6930,7 +6950,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="177" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>348</v>
       </c>
@@ -6953,7 +6973,7 @@
         <v>15.0537634408602</v>
       </c>
     </row>
-    <row r="178" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>59</v>
       </c>
@@ -6976,7 +6996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>59</v>
       </c>
@@ -6999,7 +7019,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="180" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>59</v>
       </c>
@@ -7022,7 +7042,7 @@
         <v>17.391304347826001</v>
       </c>
     </row>
-    <row r="181" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>59</v>
       </c>
@@ -7045,7 +7065,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>59</v>
       </c>
@@ -7068,7 +7088,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>353</v>
       </c>
@@ -7091,7 +7111,7 @@
         <v>16.6666666666666</v>
       </c>
     </row>
-    <row r="184" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>353</v>
       </c>
@@ -7114,7 +7134,7 @@
         <v>23.529411764705799</v>
       </c>
     </row>
-    <row r="185" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>353</v>
       </c>
@@ -7137,7 +7157,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="186" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>353</v>
       </c>
@@ -7160,7 +7180,7 @@
         <v>22.2222222222222</v>
       </c>
     </row>
-    <row r="187" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>359</v>
       </c>
@@ -7183,7 +7203,7 @@
         <v>26.229508196721302</v>
       </c>
     </row>
-    <row r="188" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>359</v>
       </c>
@@ -7206,7 +7226,7 @@
         <v>11.1111111111111</v>
       </c>
     </row>
-    <row r="189" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>359</v>
       </c>
@@ -7229,7 +7249,7 @@
         <v>5.4054054054053999</v>
       </c>
     </row>
-    <row r="190" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>67</v>
       </c>
@@ -7252,7 +7272,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="191" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>42</v>
       </c>
@@ -7275,7 +7295,7 @@
         <v>58.3333333333333</v>
       </c>
     </row>
-    <row r="192" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>42</v>
       </c>
@@ -7298,7 +7318,7 @@
         <v>21.428571428571399</v>
       </c>
     </row>
-    <row r="193" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>4</v>
       </c>
@@ -7321,7 +7341,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="194" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>4</v>
       </c>
@@ -7344,7 +7364,7 @@
         <v>14.814814814814801</v>
       </c>
     </row>
-    <row r="195" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>4</v>
       </c>
@@ -7367,7 +7387,7 @@
         <v>54.545454545454497</v>
       </c>
     </row>
-    <row r="196" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>369</v>
       </c>
@@ -7390,7 +7410,7 @@
         <v>25.806451612903199</v>
       </c>
     </row>
-    <row r="197" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>369</v>
       </c>
@@ -7413,7 +7433,7 @@
         <v>33.3333333333333</v>
       </c>
     </row>
-    <row r="198" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>369</v>
       </c>
@@ -7436,7 +7456,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="199" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>369</v>
       </c>
@@ -7459,7 +7479,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="200" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>62</v>
       </c>
@@ -7482,7 +7502,7 @@
         <v>14.814814814814801</v>
       </c>
     </row>
-    <row r="201" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>62</v>
       </c>
@@ -7505,7 +7525,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="202" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>18</v>
       </c>
@@ -7528,7 +7548,7 @@
         <v>14.285714285714199</v>
       </c>
     </row>
-    <row r="203" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>18</v>
       </c>
@@ -7551,7 +7571,7 @@
         <v>28.571428571428498</v>
       </c>
     </row>
-    <row r="204" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>18</v>
       </c>
@@ -7574,7 +7594,7 @@
         <v>18.518518518518501</v>
       </c>
     </row>
-    <row r="205" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>18</v>
       </c>
@@ -7597,7 +7617,7 @@
         <v>18.181818181818102</v>
       </c>
     </row>
-    <row r="206" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>51</v>
       </c>
@@ -7620,7 +7640,7 @@
         <v>14.285714285714199</v>
       </c>
     </row>
-    <row r="207" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>51</v>
       </c>
@@ -7643,7 +7663,7 @@
         <v>11.1111111111111</v>
       </c>
     </row>
-    <row r="208" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>51</v>
       </c>
@@ -7666,7 +7686,7 @@
         <v>16.6666666666666</v>
       </c>
     </row>
-    <row r="209" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>51</v>
       </c>
@@ -7689,7 +7709,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="210" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>377</v>
       </c>
@@ -7697,7 +7717,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="211" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>379</v>
       </c>
@@ -7705,7 +7725,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="212" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>381</v>
       </c>
@@ -7713,7 +7733,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="213" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>383</v>
       </c>
@@ -7721,7 +7741,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="214" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>385</v>
       </c>
@@ -7729,7 +7749,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="215" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>387</v>
       </c>
@@ -7737,7 +7757,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="216" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>389</v>
       </c>
@@ -7745,7 +7765,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="217" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>391</v>
       </c>
@@ -7753,7 +7773,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="218" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>393</v>
       </c>
@@ -7761,7 +7781,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="219" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>30</v>
       </c>
@@ -7784,7 +7804,7 @@
         <v>28.9156626506024</v>
       </c>
     </row>
-    <row r="220" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>30</v>
       </c>
@@ -7807,7 +7827,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="221" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>397</v>
       </c>
@@ -7830,7 +7850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>397</v>
       </c>
@@ -7853,7 +7873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>397</v>
       </c>
@@ -7876,7 +7896,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>88</v>
       </c>
@@ -7899,7 +7919,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>403</v>
       </c>
@@ -7922,7 +7942,7 @@
         <v>57.142857142857103</v>
       </c>
     </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>403</v>
       </c>
@@ -7945,7 +7965,7 @@
         <v>21.428571428571399</v>
       </c>
     </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227" s="2" t="s">
         <v>403</v>
       </c>
@@ -7968,7 +7988,7 @@
         <v>57.142857142857103</v>
       </c>
     </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>14</v>
       </c>
@@ -7991,7 +8011,7 @@
         <v>31.25</v>
       </c>
     </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>14</v>
       </c>
@@ -8014,7 +8034,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>14</v>
       </c>
@@ -8037,7 +8057,7 @@
         <v>23.529411764705799</v>
       </c>
     </row>
-    <row r="231" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>406</v>
       </c>
@@ -8045,7 +8065,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>25</v>
       </c>
@@ -8068,7 +8088,7 @@
         <v>57.142857142857103</v>
       </c>
     </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>25</v>
       </c>
@@ -8091,7 +8111,7 @@
         <v>21.428571428571399</v>
       </c>
     </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>25</v>
       </c>
@@ -8114,7 +8134,7 @@
         <v>57.142857142857103</v>
       </c>
     </row>
-    <row r="235" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>409</v>
       </c>
@@ -8122,7 +8142,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="236" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>411</v>
       </c>
@@ -8130,7 +8150,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="237" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>413</v>
       </c>
@@ -8153,7 +8173,7 @@
         <v>9.0909090909090899</v>
       </c>
     </row>
-    <row r="238" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>413</v>
       </c>
@@ -8176,7 +8196,7 @@
         <v>9.5238095238095095</v>
       </c>
     </row>
-    <row r="239" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>415</v>
       </c>
@@ -8199,7 +8219,7 @@
         <v>26.6666666666666</v>
       </c>
     </row>
-    <row r="240" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>415</v>
       </c>
@@ -8222,7 +8242,7 @@
         <v>37.037037037037003</v>
       </c>
     </row>
-    <row r="241" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>417</v>
       </c>
@@ -8245,7 +8265,7 @@
         <v>33.3333333333333</v>
       </c>
     </row>
-    <row r="242" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>64</v>
       </c>
@@ -8268,7 +8288,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="243" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>422</v>
       </c>
@@ -8276,7 +8296,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="244" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>95</v>
       </c>
@@ -8299,7 +8319,7 @@
         <v>66.6666666666666</v>
       </c>
     </row>
-    <row r="245" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>95</v>
       </c>
@@ -8322,7 +8342,7 @@
         <v>19.354838709677399</v>
       </c>
     </row>
-    <row r="246" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>17</v>
       </c>
@@ -8345,7 +8365,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="247" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>17</v>
       </c>
@@ -8368,7 +8388,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="248" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>17</v>
       </c>
@@ -8391,7 +8411,7 @@
         <v>21.052631578947299</v>
       </c>
     </row>
-    <row r="249" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>17</v>
       </c>
@@ -8414,7 +8434,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="250" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>52</v>
       </c>
@@ -8437,7 +8457,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="251" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>52</v>
       </c>
@@ -8460,7 +8480,7 @@
         <v>21.052631578947299</v>
       </c>
     </row>
-    <row r="252" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>52</v>
       </c>
@@ -8483,7 +8503,7 @@
         <v>36.363636363636303</v>
       </c>
     </row>
-    <row r="253" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>52</v>
       </c>
@@ -8506,7 +8526,7 @@
         <v>23.529411764705799</v>
       </c>
     </row>
-    <row r="254" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>76</v>
       </c>
@@ -8529,7 +8549,7 @@
         <v>72.727272727272705</v>
       </c>
     </row>
-    <row r="255" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>435</v>
       </c>
@@ -8552,7 +8572,7 @@
         <v>64.285714285714207</v>
       </c>
     </row>
-    <row r="256" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>435</v>
       </c>
@@ -8575,7 +8595,7 @@
         <v>28.571428571428498</v>
       </c>
     </row>
-    <row r="257" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>437</v>
       </c>
@@ -8583,7 +8603,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="258" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>439</v>
       </c>
@@ -8606,7 +8626,7 @@
         <v>44.4444444444444</v>
       </c>
     </row>
-    <row r="259" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>441</v>
       </c>
@@ -8629,7 +8649,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="260" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>441</v>
       </c>
@@ -8652,7 +8672,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="261" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>441</v>
       </c>
@@ -8675,7 +8695,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="262" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>441</v>
       </c>
@@ -8698,7 +8718,7 @@
         <v>8.4507042253521103</v>
       </c>
     </row>
-    <row r="263" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>441</v>
       </c>
@@ -8721,7 +8741,7 @@
         <v>35.443037974683499</v>
       </c>
     </row>
-    <row r="264" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>441</v>
       </c>
@@ -8744,7 +8764,7 @@
         <v>33.802816901408399</v>
       </c>
     </row>
-    <row r="265" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>441</v>
       </c>
@@ -8767,7 +8787,7 @@
         <v>37.931034482758598</v>
       </c>
     </row>
-    <row r="266" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>441</v>
       </c>
@@ -8790,7 +8810,7 @@
         <v>39.285714285714199</v>
       </c>
     </row>
-    <row r="267" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>441</v>
       </c>
@@ -8813,7 +8833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="268" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>450</v>
       </c>
@@ -8836,7 +8856,7 @@
         <v>25.6410256410256</v>
       </c>
     </row>
-    <row r="269" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>450</v>
       </c>
@@ -8859,7 +8879,7 @@
         <v>24.5614035087719</v>
       </c>
     </row>
-    <row r="270" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>450</v>
       </c>
@@ -8882,7 +8902,7 @@
         <v>20.689655172413701</v>
       </c>
     </row>
-    <row r="271" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>450</v>
       </c>
@@ -8905,7 +8925,7 @@
         <v>8.6956521739130395</v>
       </c>
     </row>
-    <row r="272" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>450</v>
       </c>
@@ -8928,7 +8948,7 @@
         <v>26.415094339622598</v>
       </c>
     </row>
-    <row r="273" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>452</v>
       </c>
@@ -8936,7 +8956,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="274" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>454</v>
       </c>
@@ -8944,7 +8964,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="275" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>456</v>
       </c>
@@ -8967,7 +8987,7 @@
         <v>21.276595744680801</v>
       </c>
     </row>
-    <row r="276" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>456</v>
       </c>
@@ -8990,7 +9010,7 @@
         <v>19.047619047619001</v>
       </c>
     </row>
-    <row r="277" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>456</v>
       </c>
@@ -9013,7 +9033,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="278" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>456</v>
       </c>
@@ -9036,7 +9056,7 @@
         <v>42.105263157894697</v>
       </c>
     </row>
-    <row r="279" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>458</v>
       </c>
@@ -9044,7 +9064,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="280" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>460</v>
       </c>
@@ -9052,7 +9072,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="281" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>462</v>
       </c>
@@ -9075,7 +9095,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="282" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>462</v>
       </c>
@@ -9098,7 +9118,7 @@
         <v>27.586206896551701</v>
       </c>
     </row>
-    <row r="283" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>462</v>
       </c>
@@ -9121,7 +9141,7 @@
         <v>26.315789473684202</v>
       </c>
     </row>
-    <row r="284" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>462</v>
       </c>
@@ -9144,7 +9164,7 @@
         <v>28.571428571428498</v>
       </c>
     </row>
-    <row r="285" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>462</v>
       </c>
@@ -9167,7 +9187,7 @@
         <v>26.229508196721302</v>
       </c>
     </row>
-    <row r="286" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>462</v>
       </c>
@@ -9190,7 +9210,7 @@
         <v>32.258064516128997</v>
       </c>
     </row>
-    <row r="287" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>462</v>
       </c>
@@ -9213,7 +9233,7 @@
         <v>22.2222222222222</v>
       </c>
     </row>
-    <row r="288" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>462</v>
       </c>
@@ -9236,7 +9256,7 @@
         <v>23.8095238095238</v>
       </c>
     </row>
-    <row r="289" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>11</v>
       </c>
@@ -9259,7 +9279,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="290" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>11</v>
       </c>
@@ -9282,7 +9302,7 @@
         <v>21.052631578947299</v>
       </c>
     </row>
-    <row r="291" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>11</v>
       </c>
@@ -9305,7 +9325,7 @@
         <v>21.428571428571399</v>
       </c>
     </row>
-    <row r="292" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>11</v>
       </c>
@@ -9328,7 +9348,7 @@
         <v>22.2222222222222</v>
       </c>
     </row>
-    <row r="293" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>11</v>
       </c>
@@ -9351,7 +9371,7 @@
         <v>11.764705882352899</v>
       </c>
     </row>
-    <row r="294" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>11</v>
       </c>
@@ -9374,7 +9394,7 @@
         <v>19.047619047619001</v>
       </c>
     </row>
-    <row r="295" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>11</v>
       </c>
@@ -9397,7 +9417,7 @@
         <v>23.529411764705799</v>
       </c>
     </row>
-    <row r="296" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>11</v>
       </c>
@@ -9420,7 +9440,7 @@
         <v>18.75</v>
       </c>
     </row>
-    <row r="297" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>465</v>
       </c>
@@ -9428,7 +9448,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="298" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>467</v>
       </c>
@@ -9451,7 +9471,7 @@
         <v>24.2424242424242</v>
       </c>
     </row>
-    <row r="299" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>469</v>
       </c>
@@ -9459,7 +9479,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="300" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>471</v>
       </c>
@@ -9467,7 +9487,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="301" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>7</v>
       </c>
@@ -9490,7 +9510,7 @@
         <v>42.857142857142797</v>
       </c>
     </row>
-    <row r="302" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>475</v>
       </c>
@@ -9498,7 +9518,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="303" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>477</v>
       </c>
@@ -9506,7 +9526,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="304" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>479</v>
       </c>
@@ -9514,7 +9534,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="305" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>481</v>
       </c>
@@ -9522,7 +9542,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="306" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>483</v>
       </c>
@@ -9530,7 +9550,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="307" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>485</v>
       </c>
@@ -9553,7 +9573,7 @@
         <v>30.188679245283002</v>
       </c>
     </row>
-    <row r="308" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>485</v>
       </c>
@@ -9576,7 +9596,7 @@
         <v>31.746031746031701</v>
       </c>
     </row>
-    <row r="309" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>485</v>
       </c>
@@ -9599,7 +9619,7 @@
         <v>23.076923076922998</v>
       </c>
     </row>
-    <row r="310" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>487</v>
       </c>
@@ -9607,7 +9627,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="311" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>489</v>
       </c>
@@ -9615,7 +9635,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="312" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>21</v>
       </c>
@@ -9638,7 +9658,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="313" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>80</v>
       </c>
@@ -9661,7 +9681,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="314" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>31</v>
       </c>
@@ -9684,7 +9704,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="315" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
         <v>86</v>
       </c>
@@ -9707,7 +9727,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="316" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>498</v>
       </c>
@@ -9715,7 +9735,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="317" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>500</v>
       </c>
@@ -9738,7 +9758,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="318" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
         <v>500</v>
       </c>
@@ -9761,7 +9781,7 @@
         <v>41.379310344827502</v>
       </c>
     </row>
-    <row r="319" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>500</v>
       </c>
@@ -9784,7 +9804,7 @@
         <v>32.258064516128997</v>
       </c>
     </row>
-    <row r="320" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
         <v>505</v>
       </c>
@@ -9807,7 +9827,7 @@
         <v>12.1212121212121</v>
       </c>
     </row>
-    <row r="321" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>505</v>
       </c>
@@ -9830,7 +9850,7 @@
         <v>46.6666666666666</v>
       </c>
     </row>
-    <row r="322" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>505</v>
       </c>
@@ -9853,7 +9873,7 @@
         <v>28.571428571428498</v>
       </c>
     </row>
-    <row r="323" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
         <v>69</v>
       </c>
@@ -9876,7 +9896,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="324" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>49</v>
       </c>
@@ -9899,7 +9919,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="325" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>49</v>
       </c>
@@ -9922,7 +9942,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="326" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
         <v>49</v>
       </c>
@@ -9945,7 +9965,7 @@
         <v>22.2222222222222</v>
       </c>
     </row>
-    <row r="327" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>49</v>
       </c>
@@ -9968,7 +9988,7 @@
         <v>19.354838709677399</v>
       </c>
     </row>
-    <row r="328" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
         <v>90</v>
       </c>
@@ -9991,7 +10011,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="329" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>82</v>
       </c>
@@ -10014,7 +10034,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="330" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>515</v>
       </c>
@@ -10022,7 +10042,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="331" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
         <v>517</v>
       </c>
@@ -10030,7 +10050,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="332" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
         <v>519</v>
       </c>
@@ -10038,7 +10058,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="333" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
         <v>521</v>
       </c>
@@ -10046,7 +10066,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="334" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
         <v>523</v>
       </c>
@@ -10054,7 +10074,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="335" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
         <v>525</v>
       </c>
@@ -10062,7 +10082,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="336" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
         <v>527</v>
       </c>
@@ -10070,7 +10090,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="337" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>529</v>
       </c>
@@ -10078,7 +10098,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="338" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>531</v>
       </c>
@@ -10086,7 +10106,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="339" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
         <v>533</v>
       </c>
@@ -10094,7 +10114,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="340" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
         <v>535</v>
       </c>
@@ -10102,44 +10122,44 @@
         <v>536</v>
       </c>
     </row>
-    <row r="341" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>96</v>
       </c>
       <c r="B341">
-        <v>1147</v>
+        <v>4866</v>
       </c>
       <c r="C341">
-        <v>18014.560000000001</v>
+        <v>11512.09</v>
       </c>
       <c r="D341" t="s">
         <v>537</v>
       </c>
       <c r="E341" t="s">
-        <v>538</v>
+        <v>281</v>
       </c>
       <c r="F341">
-        <v>52.173913043478201</v>
+        <v>100</v>
       </c>
       <c r="G341">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="342" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="342" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
-        <v>96</v>
+        <v>16</v>
       </c>
       <c r="B342">
-        <v>4866</v>
+        <v>19397</v>
       </c>
       <c r="C342">
-        <v>11512.09</v>
+        <v>77.88</v>
       </c>
       <c r="D342" t="s">
-        <v>537</v>
+        <v>227</v>
       </c>
       <c r="E342" t="s">
-        <v>281</v>
+        <v>228</v>
       </c>
       <c r="F342">
         <v>100</v>
@@ -10148,7 +10168,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="343" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
         <v>539</v>
       </c>
@@ -10156,7 +10176,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="344" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
         <v>541</v>
       </c>
@@ -10164,7 +10184,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="345" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>97</v>
       </c>
@@ -10187,7 +10207,7 @@
         <v>30.303030303030202</v>
       </c>
     </row>
-    <row r="346" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
         <v>97</v>
       </c>
@@ -10210,7 +10230,7 @@
         <v>26.6666666666666</v>
       </c>
     </row>
-    <row r="347" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
         <v>97</v>
       </c>
@@ -10233,7 +10253,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="348" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
         <v>60</v>
       </c>
@@ -10256,7 +10276,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="349" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
         <v>22</v>
       </c>
@@ -10279,7 +10299,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="350" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
         <v>56</v>
       </c>
@@ -10302,7 +10322,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="351" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
         <v>56</v>
       </c>
@@ -10325,7 +10345,7 @@
         <v>10.5263157894736</v>
       </c>
     </row>
-    <row r="352" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
         <v>56</v>
       </c>
@@ -10348,7 +10368,7 @@
         <v>14.285714285714199</v>
       </c>
     </row>
-    <row r="353" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
         <v>56</v>
       </c>
@@ -10371,7 +10391,7 @@
         <v>18.181818181818102</v>
       </c>
     </row>
-    <row r="354" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
         <v>56</v>
       </c>
@@ -10394,7 +10414,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="355" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
         <v>56</v>
       </c>
@@ -10417,7 +10437,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="356" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>56</v>
       </c>
@@ -10440,7 +10460,7 @@
         <v>19.047619047619001</v>
       </c>
     </row>
-    <row r="357" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
         <v>56</v>
       </c>
@@ -10463,7 +10483,7 @@
         <v>11.764705882352899</v>
       </c>
     </row>
-    <row r="358" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
         <v>56</v>
       </c>
@@ -10486,7 +10506,7 @@
         <v>18.75</v>
       </c>
     </row>
-    <row r="359" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
         <v>12</v>
       </c>
@@ -10509,7 +10529,7 @@
         <v>8.3333333333333197</v>
       </c>
     </row>
-    <row r="360" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
         <v>12</v>
       </c>
@@ -10532,7 +10552,7 @@
         <v>12.1212121212121</v>
       </c>
     </row>
-    <row r="361" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
         <v>12</v>
       </c>
@@ -10555,7 +10575,7 @@
         <v>29.629629629629601</v>
       </c>
     </row>
-    <row r="362" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
         <v>12</v>
       </c>
@@ -10578,7 +10598,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="363" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
         <v>12</v>
       </c>
@@ -10601,7 +10621,7 @@
         <v>18.181818181818102</v>
       </c>
     </row>
-    <row r="364" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
         <v>12</v>
       </c>
@@ -10624,7 +10644,7 @@
         <v>21.6216216216216</v>
       </c>
     </row>
-    <row r="365" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
         <v>550</v>
       </c>
@@ -10647,7 +10667,7 @@
         <v>22.2222222222222</v>
       </c>
     </row>
-    <row r="366" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
         <v>13</v>
       </c>
@@ -10670,7 +10690,7 @@
         <v>17.391304347826001</v>
       </c>
     </row>
-    <row r="367" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
         <v>13</v>
       </c>
@@ -10693,7 +10713,7 @@
         <v>18.75</v>
       </c>
     </row>
-    <row r="368" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
         <v>13</v>
       </c>
@@ -10716,7 +10736,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="369" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
         <v>13</v>
       </c>
@@ -10739,7 +10759,7 @@
         <v>29.629629629629601</v>
       </c>
     </row>
-    <row r="370" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
         <v>13</v>
       </c>
@@ -10762,7 +10782,7 @@
         <v>27.272727272727199</v>
       </c>
     </row>
-    <row r="371" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
         <v>13</v>
       </c>
@@ -10785,7 +10805,7 @@
         <v>21.818181818181799</v>
       </c>
     </row>
-    <row r="372" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
         <v>13</v>
       </c>
@@ -10808,7 +10828,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="373" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
         <v>13</v>
       </c>
@@ -10831,7 +10851,7 @@
         <v>19.047619047619001</v>
       </c>
     </row>
-    <row r="374" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
         <v>13</v>
       </c>
@@ -10854,7 +10874,7 @@
         <v>22.2222222222222</v>
       </c>
     </row>
-    <row r="375" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
         <v>75</v>
       </c>
@@ -10877,7 +10897,7 @@
         <v>26.086956521739101</v>
       </c>
     </row>
-    <row r="376" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
         <v>75</v>
       </c>
@@ -10900,7 +10920,7 @@
         <v>18.181818181818102</v>
       </c>
     </row>
-    <row r="377" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
         <v>75</v>
       </c>
@@ -10923,7 +10943,7 @@
         <v>19.354838709677399</v>
       </c>
     </row>
-    <row r="378" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
         <v>75</v>
       </c>
@@ -10946,7 +10966,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="379" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
         <v>75</v>
       </c>
@@ -10969,7 +10989,7 @@
         <v>19.047619047619001</v>
       </c>
     </row>
-    <row r="380" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
         <v>75</v>
       </c>
@@ -10992,7 +11012,7 @@
         <v>18.518518518518501</v>
       </c>
     </row>
-    <row r="381" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
         <v>75</v>
       </c>
@@ -11015,7 +11035,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="382" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
         <v>75</v>
       </c>
@@ -11038,7 +11058,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="383" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
         <v>75</v>
       </c>
@@ -11061,7 +11081,7 @@
         <v>17.1428571428571</v>
       </c>
     </row>
-    <row r="384" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
         <v>28</v>
       </c>
@@ -11084,7 +11104,7 @@
         <v>35.294117647058798</v>
       </c>
     </row>
-    <row r="385" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
         <v>28</v>
       </c>
@@ -11107,7 +11127,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="386" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
         <v>558</v>
       </c>
@@ -11115,7 +11135,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="387" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
         <v>560</v>
       </c>
@@ -11123,7 +11143,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="388" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
         <v>562</v>
       </c>
@@ -11146,7 +11166,7 @@
         <v>6.8965517241379297</v>
       </c>
     </row>
-    <row r="389" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
         <v>562</v>
       </c>
@@ -11169,7 +11189,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="390" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
         <v>562</v>
       </c>
@@ -11192,7 +11212,7 @@
         <v>32.558139534883701</v>
       </c>
     </row>
-    <row r="391" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
         <v>61</v>
       </c>
@@ -11215,7 +11235,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="392" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
         <v>61</v>
       </c>
@@ -11238,7 +11258,7 @@
         <v>23.2558139534883</v>
       </c>
     </row>
-    <row r="393" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
         <v>566</v>
       </c>
@@ -11261,7 +11281,7 @@
         <v>10.1694915254237</v>
       </c>
     </row>
-    <row r="394" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
         <v>566</v>
       </c>
@@ -11284,7 +11304,7 @@
         <v>34.567901234567898</v>
       </c>
     </row>
-    <row r="395" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
         <v>566</v>
       </c>
@@ -11307,7 +11327,7 @@
         <v>27.272727272727199</v>
       </c>
     </row>
-    <row r="396" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
         <v>568</v>
       </c>
@@ -11315,7 +11335,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="397" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
         <v>570</v>
       </c>
@@ -11323,7 +11343,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="398" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
         <v>572</v>
       </c>
@@ -11331,7 +11351,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="399" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
         <v>574</v>
       </c>
@@ -11339,7 +11359,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="400" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
         <v>576</v>
       </c>
@@ -11347,7 +11367,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="401" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
         <v>578</v>
       </c>
@@ -11355,7 +11375,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="402" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
         <v>580</v>
       </c>
@@ -11363,7 +11383,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="403" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
         <v>78</v>
       </c>
@@ -11386,7 +11406,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="404" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
         <v>582</v>
       </c>
@@ -11394,7 +11414,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="405" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
         <v>584</v>
       </c>
@@ -11417,7 +11437,7 @@
         <v>9.0909090909090899</v>
       </c>
     </row>
-    <row r="406" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
         <v>586</v>
       </c>
@@ -11425,7 +11445,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="407" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
         <v>3</v>
       </c>
@@ -11448,7 +11468,7 @@
         <v>28.571428571428498</v>
       </c>
     </row>
-    <row r="408" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
         <v>3</v>
       </c>
@@ -11471,7 +11491,7 @@
         <v>28.571428571428498</v>
       </c>
     </row>
-    <row r="409" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
         <v>590</v>
       </c>
@@ -11479,7 +11499,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="410" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
         <v>592</v>
       </c>
@@ -11502,7 +11522,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="411" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
         <v>595</v>
       </c>
@@ -11510,7 +11530,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="412" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
         <v>597</v>
       </c>
@@ -11518,7 +11538,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="413" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
         <v>599</v>
       </c>
@@ -11526,7 +11546,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="414" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
         <v>601</v>
       </c>
@@ -11549,7 +11569,7 @@
         <v>33.3333333333333</v>
       </c>
     </row>
-    <row r="415" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
         <v>63</v>
       </c>
@@ -11572,7 +11592,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="416" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
         <v>604</v>
       </c>
@@ -11595,7 +11615,7 @@
         <v>27.7777777777777</v>
       </c>
     </row>
-    <row r="417" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
         <v>66</v>
       </c>
@@ -11618,7 +11638,7 @@
         <v>28.571428571428498</v>
       </c>
     </row>
-    <row r="418" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
         <v>66</v>
       </c>
@@ -11641,7 +11661,7 @@
         <v>72.727272727272705</v>
       </c>
     </row>
-    <row r="419" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
         <v>66</v>
       </c>
@@ -11664,7 +11684,7 @@
         <v>31.034482758620602</v>
       </c>
     </row>
-    <row r="420" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
         <v>66</v>
       </c>
@@ -11687,7 +11707,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="421" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
         <v>66</v>
       </c>
@@ -11710,7 +11730,7 @@
         <v>20.8333333333333</v>
       </c>
     </row>
-    <row r="422" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
         <v>66</v>
       </c>
@@ -11733,7 +11753,7 @@
         <v>28.571428571428498</v>
       </c>
     </row>
-    <row r="423" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
         <v>66</v>
       </c>
@@ -11756,7 +11776,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="424" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
         <v>66</v>
       </c>
@@ -11779,7 +11799,7 @@
         <v>22.727272727272702</v>
       </c>
     </row>
-    <row r="425" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
         <v>66</v>
       </c>
@@ -11802,7 +11822,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="426" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="426" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
         <v>66</v>
       </c>
@@ -11825,7 +11845,7 @@
         <v>25.806451612903199</v>
       </c>
     </row>
-    <row r="427" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
         <v>66</v>
       </c>
@@ -11848,7 +11868,7 @@
         <v>31.25</v>
       </c>
     </row>
-    <row r="428" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="428" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
         <v>608</v>
       </c>
@@ -11871,7 +11891,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="429" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="429" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
         <v>608</v>
       </c>
@@ -11894,7 +11914,7 @@
         <v>21.052631578947299</v>
       </c>
     </row>
-    <row r="430" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
         <v>612</v>
       </c>
@@ -11902,7 +11922,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="431" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="431" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
         <v>614</v>
       </c>
@@ -11910,7 +11930,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="432" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="432" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
         <v>616</v>
       </c>
@@ -11933,7 +11953,7 @@
         <v>20.408163265306101</v>
       </c>
     </row>
-    <row r="433" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="433" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
         <v>616</v>
       </c>
@@ -11956,7 +11976,7 @@
         <v>18.867924528301799</v>
       </c>
     </row>
-    <row r="434" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
         <v>618</v>
       </c>
@@ -11979,7 +11999,7 @@
         <v>14.814814814814801</v>
       </c>
     </row>
-    <row r="435" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
         <v>621</v>
       </c>
@@ -11987,7 +12007,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="436" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
         <v>623</v>
       </c>
@@ -12010,7 +12030,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="437" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="437" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
         <v>623</v>
       </c>
@@ -12033,7 +12053,7 @@
         <v>51.851851851851798</v>
       </c>
     </row>
-    <row r="438" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="438" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
         <v>23</v>
       </c>
@@ -12056,7 +12076,7 @@
         <v>10.5263157894736</v>
       </c>
     </row>
-    <row r="439" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="439" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
         <v>23</v>
       </c>
@@ -12079,7 +12099,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="440" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="440" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
         <v>626</v>
       </c>
@@ -12102,7 +12122,7 @@
         <v>40.909090909090899</v>
       </c>
     </row>
-    <row r="441" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="441" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
         <v>626</v>
       </c>
@@ -12125,7 +12145,7 @@
         <v>55.172413793103402</v>
       </c>
     </row>
-    <row r="442" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
         <v>628</v>
       </c>
@@ -12133,7 +12153,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="443" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
         <v>630</v>
       </c>
@@ -12141,7 +12161,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="444" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
         <v>34</v>
       </c>
@@ -12164,7 +12184,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="445" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="445" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
         <v>634</v>
       </c>
@@ -12172,7 +12192,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="446" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="446" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
         <v>35</v>
       </c>
@@ -12195,7 +12215,7 @@
         <v>37.5</v>
       </c>
     </row>
-    <row r="447" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="447" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
         <v>638</v>
       </c>
@@ -12203,7 +12223,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="448" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="448" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
         <v>83</v>
       </c>
@@ -12226,7 +12246,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="449" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="449" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
         <v>642</v>
       </c>
@@ -12234,7 +12254,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="450" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="450" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
         <v>46</v>
       </c>
@@ -12257,7 +12277,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="451" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="451" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
         <v>646</v>
       </c>
@@ -12265,7 +12285,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="452" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="452" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
         <v>73</v>
       </c>
@@ -12288,7 +12308,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="453" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="453" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
         <v>650</v>
       </c>
@@ -12296,7 +12316,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="454" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="454" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
         <v>652</v>
       </c>
@@ -12304,7 +12324,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="455" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="455" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
         <v>654</v>
       </c>
@@ -12327,7 +12347,7 @@
         <v>29.268292682926798</v>
       </c>
     </row>
-    <row r="456" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="456" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
         <v>656</v>
       </c>
@@ -12350,7 +12370,7 @@
         <v>22.2222222222222</v>
       </c>
     </row>
-    <row r="457" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="457" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
         <v>656</v>
       </c>
@@ -12373,7 +12393,7 @@
         <v>26.315789473684202</v>
       </c>
     </row>
-    <row r="458" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="458" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
         <v>19</v>
       </c>
@@ -12396,7 +12416,7 @@
         <v>18.604651162790699</v>
       </c>
     </row>
-    <row r="459" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="459" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
         <v>19</v>
       </c>
@@ -12419,7 +12439,7 @@
         <v>20.5128205128205</v>
       </c>
     </row>
-    <row r="460" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="460" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
         <v>19</v>
       </c>
@@ -12442,7 +12462,7 @@
         <v>20.689655172413701</v>
       </c>
     </row>
-    <row r="461" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="461" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
         <v>19</v>
       </c>
@@ -12465,7 +12485,7 @@
         <v>23.529411764705799</v>
       </c>
     </row>
-    <row r="462" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="462" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
         <v>20</v>
       </c>
@@ -12488,7 +12508,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="463" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="463" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
         <v>20</v>
       </c>
@@ -12511,7 +12531,7 @@
         <v>28.571428571428498</v>
       </c>
     </row>
-    <row r="464" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="464" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
         <v>20</v>
       </c>
@@ -12534,7 +12554,7 @@
         <v>22.857142857142801</v>
       </c>
     </row>
-    <row r="465" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="465" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
         <v>20</v>
       </c>
@@ -12557,7 +12577,7 @@
         <v>33.3333333333333</v>
       </c>
     </row>
-    <row r="466" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="466" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
         <v>20</v>
       </c>
@@ -12580,7 +12600,7 @@
         <v>22.857142857142801</v>
       </c>
     </row>
-    <row r="467" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="467" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
         <v>20</v>
       </c>
@@ -12603,7 +12623,7 @@
         <v>29.629629629629601</v>
       </c>
     </row>
-    <row r="468" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="468" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
         <v>20</v>
       </c>
@@ -12626,7 +12646,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="469" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="469" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
         <v>20</v>
       </c>
@@ -12649,7 +12669,7 @@
         <v>31.578947368421002</v>
       </c>
     </row>
-    <row r="470" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="470" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
         <v>92</v>
       </c>
@@ -12672,7 +12692,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="471" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="471" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
         <v>92</v>
       </c>
@@ -12695,7 +12715,7 @@
         <v>33.3333333333333</v>
       </c>
     </row>
-    <row r="472" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="472" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
         <v>92</v>
       </c>
@@ -12718,7 +12738,7 @@
         <v>15.6862745098039</v>
       </c>
     </row>
-    <row r="473" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="473" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
         <v>92</v>
       </c>
@@ -12741,7 +12761,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="474" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="474" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
         <v>89</v>
       </c>
@@ -12764,7 +12784,7 @@
         <v>28.571428571428498</v>
       </c>
     </row>
-    <row r="475" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="475" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
         <v>89</v>
       </c>
@@ -12787,7 +12807,7 @@
         <v>19.354838709677399</v>
       </c>
     </row>
-    <row r="476" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="476" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
         <v>89</v>
       </c>
@@ -12810,7 +12830,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="477" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="477" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
         <v>89</v>
       </c>
@@ -12833,7 +12853,7 @@
         <v>29.411764705882302</v>
       </c>
     </row>
-    <row r="478" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="478" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
         <v>89</v>
       </c>
@@ -12856,7 +12876,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="479" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="479" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
         <v>89</v>
       </c>
@@ -12879,7 +12899,7 @@
         <v>21.6216216216216</v>
       </c>
     </row>
-    <row r="480" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="480" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
         <v>89</v>
       </c>
@@ -12902,7 +12922,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="481" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="481" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
         <v>89</v>
       </c>
@@ -12925,7 +12945,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="482" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="482" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
         <v>36</v>
       </c>
@@ -12948,7 +12968,7 @@
         <v>28.571428571428498</v>
       </c>
     </row>
-    <row r="483" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="483" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
         <v>36</v>
       </c>
@@ -12971,7 +12991,7 @@
         <v>19.354838709677399</v>
       </c>
     </row>
-    <row r="484" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="484" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
         <v>36</v>
       </c>
@@ -12994,7 +13014,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="485" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="485" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
         <v>36</v>
       </c>
@@ -13017,7 +13037,7 @@
         <v>29.411764705882302</v>
       </c>
     </row>
-    <row r="486" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="486" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
         <v>36</v>
       </c>
@@ -13040,7 +13060,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="487" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="487" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
         <v>36</v>
       </c>
@@ -13063,7 +13083,7 @@
         <v>21.6216216216216</v>
       </c>
     </row>
-    <row r="488" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="488" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
         <v>36</v>
       </c>
@@ -13086,7 +13106,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="489" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="489" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
         <v>36</v>
       </c>
@@ -13109,7 +13129,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="490" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="490" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
         <v>24</v>
       </c>
@@ -13132,7 +13152,7 @@
         <v>21.739130434782599</v>
       </c>
     </row>
-    <row r="491" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="491" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
         <v>24</v>
       </c>
@@ -13155,7 +13175,7 @@
         <v>33.3333333333333</v>
       </c>
     </row>
-    <row r="492" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="492" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
         <v>24</v>
       </c>
@@ -13178,7 +13198,7 @@
         <v>23.529411764705799</v>
       </c>
     </row>
-    <row r="493" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="493" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
         <v>24</v>
       </c>
@@ -13201,7 +13221,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="494" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="494" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
         <v>24</v>
       </c>
@@ -13224,7 +13244,7 @@
         <v>23.529411764705799</v>
       </c>
     </row>
-    <row r="495" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="495" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
         <v>24</v>
       </c>
@@ -13247,7 +13267,7 @@
         <v>30.769230769230699</v>
       </c>
     </row>
-    <row r="496" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="496" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
         <v>24</v>
       </c>
@@ -13270,7 +13290,7 @@
         <v>33.3333333333333</v>
       </c>
     </row>
-    <row r="497" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="497" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
         <v>24</v>
       </c>
@@ -13293,7 +13313,7 @@
         <v>27.586206896551701</v>
       </c>
     </row>
-    <row r="498" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="498" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
         <v>24</v>
       </c>
@@ -13316,7 +13336,7 @@
         <v>27.027027027027</v>
       </c>
     </row>
-    <row r="499" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="499" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
         <v>27</v>
       </c>
@@ -13339,7 +13359,7 @@
         <v>7.4074074074074003</v>
       </c>
     </row>
-    <row r="500" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="500" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
         <v>27</v>
       </c>
@@ -13362,7 +13382,7 @@
         <v>19.047619047619001</v>
       </c>
     </row>
-    <row r="501" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="501" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
         <v>27</v>
       </c>
@@ -13385,7 +13405,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="502" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="502" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
         <v>27</v>
       </c>
@@ -13408,7 +13428,7 @@
         <v>26.086956521739101</v>
       </c>
     </row>
-    <row r="503" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="503" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
         <v>27</v>
       </c>
@@ -13431,7 +13451,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="504" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="504" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
         <v>27</v>
       </c>
@@ -13454,7 +13474,7 @@
         <v>7.6923076923076898</v>
       </c>
     </row>
-    <row r="505" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="505" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
         <v>10</v>
       </c>
@@ -13477,7 +13497,7 @@
         <v>26.6666666666666</v>
       </c>
     </row>
-    <row r="506" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="506" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
         <v>10</v>
       </c>
@@ -13500,7 +13520,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="507" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="507" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
         <v>674</v>
       </c>
@@ -13523,7 +13543,7 @@
         <v>59.259259259259203</v>
       </c>
     </row>
-    <row r="508" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="508" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
         <v>9</v>
       </c>
@@ -13546,7 +13566,7 @@
         <v>13.953488372093</v>
       </c>
     </row>
-    <row r="509" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="509" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
         <v>9</v>
       </c>
@@ -13569,7 +13589,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="510" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="510" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
         <v>9</v>
       </c>
@@ -13592,7 +13612,7 @@
         <v>26.6666666666666</v>
       </c>
     </row>
-    <row r="511" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="511" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
         <v>33</v>
       </c>
@@ -13615,7 +13635,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="512" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="512" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
         <v>65</v>
       </c>
@@ -13638,7 +13658,7 @@
         <v>64.705882352941103</v>
       </c>
     </row>
-    <row r="513" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="513" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
         <v>682</v>
       </c>
@@ -13646,7 +13666,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="514" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="514" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
         <v>684</v>
       </c>
@@ -13669,7 +13689,7 @@
         <v>51.428571428571402</v>
       </c>
     </row>
-    <row r="515" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="515" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
         <v>687</v>
       </c>
@@ -13677,7 +13697,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="516" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="516" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
         <v>689</v>
       </c>
@@ -13685,7 +13705,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="517" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="517" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
         <v>691</v>
       </c>
@@ -13693,7 +13713,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="518" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="518" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
         <v>693</v>
       </c>
@@ -13701,7 +13721,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="519" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="519" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
         <v>695</v>
       </c>
@@ -13709,7 +13729,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="520" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="520" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
         <v>5</v>
       </c>
@@ -13732,7 +13752,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="521" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="521" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
         <v>5</v>
       </c>
@@ -13755,7 +13775,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="522" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="522" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
         <v>700</v>
       </c>
@@ -13778,7 +13798,7 @@
         <v>22.2222222222222</v>
       </c>
     </row>
-    <row r="523" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="523" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
         <v>700</v>
       </c>
@@ -13801,7 +13821,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="524" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="524" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
         <v>700</v>
       </c>
@@ -13824,7 +13844,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="525" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="525" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
         <v>702</v>
       </c>
@@ -13847,7 +13867,7 @@
         <v>23.076923076922998</v>
       </c>
     </row>
-    <row r="526" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="526" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
         <v>702</v>
       </c>
@@ -13870,7 +13890,7 @@
         <v>16.6666666666666</v>
       </c>
     </row>
-    <row r="527" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="527" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
         <v>704</v>
       </c>
@@ -13893,7 +13913,7 @@
         <v>28.571428571428498</v>
       </c>
     </row>
-    <row r="528" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="528" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
         <v>706</v>
       </c>
@@ -13901,7 +13921,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="529" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="529" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
         <v>708</v>
       </c>
@@ -13909,7 +13929,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="530" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="530" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
         <v>710</v>
       </c>
@@ -13917,7 +13937,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="531" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="531" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="B531">
         <v>25155</v>
       </c>
@@ -13925,7 +13945,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="532" spans="1:5" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="532" spans="1:5" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B532" s="1">
         <v>29389</v>
       </c>
@@ -13933,7 +13953,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="533" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="533" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="B533">
         <v>33878</v>
       </c>
@@ -13941,7 +13961,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="534" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="534" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="B534">
         <v>28456</v>
       </c>
@@ -13949,7 +13969,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="535" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="535" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="B535">
         <v>28455</v>
       </c>
@@ -13957,7 +13977,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="536" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="536" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="B536">
         <v>29381</v>
       </c>
@@ -13965,7 +13985,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="537" spans="1:5" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="537" spans="1:5" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B537" s="1">
         <v>8600</v>
       </c>
@@ -13973,7 +13993,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="538" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="538" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="B538">
         <v>3414</v>
       </c>
@@ -13981,7 +14001,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="539" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="539" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="B539">
         <v>31795</v>
       </c>
@@ -13989,7 +14009,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="540" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="540" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="B540">
         <v>11743</v>
       </c>
@@ -13997,7 +14017,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="541" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="541" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="B541">
         <v>6425</v>
       </c>
@@ -14005,7 +14025,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="542" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="542" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="B542">
         <v>29897</v>
       </c>
@@ -14013,7 +14033,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="543" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="543" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="B543">
         <v>34791</v>
       </c>
@@ -14021,7 +14041,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="544" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="544" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="B544">
         <v>11623</v>
       </c>
@@ -14029,7 +14049,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="545" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="545" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="B545">
         <v>32987</v>
       </c>
@@ -14037,7 +14057,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="546" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="546" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="B546">
         <v>2794</v>
       </c>
@@ -14045,7 +14065,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="547" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="547" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="B547">
         <v>2371</v>
       </c>
@@ -14053,7 +14073,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="548" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="548" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="B548">
         <v>4922</v>
       </c>
@@ -14061,7 +14081,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="549" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="549" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="B549">
         <v>10537</v>
       </c>
@@ -14069,7 +14089,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="550" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="550" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="B550">
         <v>11811</v>
       </c>
@@ -14077,7 +14097,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="551" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="551" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="B551">
         <v>28947</v>
       </c>
@@ -14085,7 +14105,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="552" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="552" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="B552">
         <v>3219</v>
       </c>
@@ -14093,7 +14113,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="553" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="553" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="B553">
         <v>11649</v>
       </c>
@@ -14101,7 +14121,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="554" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="554" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="B554">
         <v>4819</v>
       </c>
@@ -14109,7 +14129,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="555" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="555" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="B555">
         <v>7825</v>
       </c>
@@ -14117,7 +14137,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="556" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="556" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="B556">
         <v>6363</v>
       </c>
@@ -14125,7 +14145,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="557" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="557" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="B557">
         <v>2396</v>
       </c>
@@ -14133,7 +14153,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="558" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="558" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="B558">
         <v>7325</v>
       </c>
@@ -14141,7 +14161,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="559" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="559" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="B559">
         <v>5649</v>
       </c>
@@ -14149,7 +14169,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="560" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="560" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="B560">
         <v>1541</v>
       </c>
@@ -14157,7 +14177,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="561" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="561" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="B561">
         <v>7154</v>
       </c>
@@ -14165,7 +14185,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="562" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="562" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="B562">
         <v>701</v>
       </c>
@@ -14173,7 +14193,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="563" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="563" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="B563">
         <v>11158</v>
       </c>
@@ -14181,7 +14201,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="564" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="564" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="B564">
         <v>7080</v>
       </c>
@@ -14189,7 +14209,7 @@
         <v>744</v>
       </c>
     </row>
-    <row r="565" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="565" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="B565">
         <v>4799</v>
       </c>
@@ -14197,7 +14217,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="566" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="566" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="B566">
         <v>11787</v>
       </c>
@@ -14205,7 +14225,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="567" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="567" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="B567">
         <v>7674</v>
       </c>
@@ -14213,7 +14233,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="568" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="568" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="B568">
         <v>7675</v>
       </c>
@@ -14221,7 +14241,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="569" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="569" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="B569">
         <v>6366</v>
       </c>
@@ -14229,7 +14249,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="570" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="570" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="B570">
         <v>4761</v>
       </c>
@@ -14237,7 +14257,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="571" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="571" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="B571">
         <v>11713</v>
       </c>
@@ -14245,7 +14265,7 @@
         <v>751</v>
       </c>
     </row>
-    <row r="572" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="572" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="B572">
         <v>11372</v>
       </c>
@@ -14253,7 +14273,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="573" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="573" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="B573">
         <v>2544</v>
       </c>
@@ -14261,7 +14281,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="574" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="574" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="B574">
         <v>4978</v>
       </c>
@@ -14269,7 +14289,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="575" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="575" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="B575">
         <v>3032</v>
       </c>
@@ -14277,7 +14297,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="576" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="576" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="B576">
         <v>31796</v>
       </c>
@@ -14285,7 +14305,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="577" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="577" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="B577">
         <v>32448</v>
       </c>
@@ -14293,7 +14313,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="578" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="578" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="B578">
         <v>10418</v>
       </c>
@@ -14301,7 +14321,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="579" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="579" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="B579">
         <v>21</v>
       </c>
@@ -14309,7 +14329,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="580" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="580" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="B580">
         <v>5183</v>
       </c>
@@ -14317,7 +14337,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="581" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="581" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="B581">
         <v>4472</v>
       </c>
@@ -14325,7 +14345,7 @@
         <v>761</v>
       </c>
     </row>
-    <row r="582" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="582" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="B582">
         <v>23568</v>
       </c>
@@ -14333,7 +14353,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="583" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="583" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="B583">
         <v>276</v>
       </c>
@@ -14341,7 +14361,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="584" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="584" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="B584">
         <v>11004</v>
       </c>
@@ -14349,7 +14369,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="585" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="585" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="B585">
         <v>2741</v>
       </c>
@@ -14357,7 +14377,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="586" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="586" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="B586">
         <v>27784</v>
       </c>
@@ -14365,7 +14385,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="587" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="587" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="B587">
         <v>28578</v>
       </c>
@@ -14373,7 +14393,7 @@
         <v>767</v>
       </c>
     </row>
-    <row r="588" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="588" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="B588">
         <v>24203</v>
       </c>
@@ -14381,7 +14401,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="589" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="589" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="B589">
         <v>4717</v>
       </c>
@@ -14391,13 +14411,14 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:G589" xr:uid="{556460DC-71F1-43FF-BD31-36D25365B781}">
-    <filterColumn colId="0">
+    <filterColumn colId="3">
       <filters>
-        <filter val="MB-MAIN-0898e255"/>
-        <filter val="MB-MAIN-be5b3dc8"/>
-        <filter val="MB-MAIN-da0b5c3d"/>
+        <filter val="Thompson (T-1 and T-3)"/>
       </filters>
     </filterColumn>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A92:G342">
+      <sortCondition ref="B1:B589"/>
+    </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
